--- a/Reports/VALR/ValrPro_Testing.xlsx
+++ b/Reports/VALR/ValrPro_Testing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="353">
   <si>
     <t xml:space="preserve">Tester : </t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>TC-010</t>
+  </si>
+  <si>
+    <t>Unsolved</t>
   </si>
   <si>
     <t>TC-011</t>
@@ -1035,6 +1038,103 @@
   </si>
   <si>
     <t>https://jam.dev/c/5aaba718-3a6c-4865-9743-0b788bbf1907</t>
+  </si>
+  <si>
+    <t>VA Form</t>
+  </si>
+  <si>
+    <t>gulf_war_location</t>
+  </si>
+  <si>
+    <t>Missing war location in chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 9th steps </t>
+  </si>
+  <si>
+    <t>Email : bijoymamud.09@gmail.com
+Pass : 12345678</t>
+  </si>
+  <si>
+    <t>Accurate locations of U.S. involvement in wars need to be displayed for veterans to choose their fighting regions.</t>
+  </si>
+  <si>
+    <t>The United States has conflicts with various countries, but Gulf War-related risk locations are the only ones highlighted, potentially causing veterans to miss out on VA benefits.</t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/0a02aaf8-8e4e-407a-9ead-21cf454d357e</t>
+  </si>
+  <si>
+    <t>Unsolve</t>
+  </si>
+  <si>
+    <t>mental_health_info</t>
+  </si>
+  <si>
+    <t>Work period time is not clearly specified as per day or total service hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 12th steps </t>
+  </si>
+  <si>
+    <t>Veterans' work period should be clearly specified as either daily hours or total service hours.</t>
+  </si>
+  <si>
+    <t>The lack of proper information has been noticed, which can sometimes lead to confusion for some veterans.</t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/4fedc7b2-3f23-42bf-b95c-8315a5122b20</t>
+  </si>
+  <si>
+    <t>mental_health_details</t>
+  </si>
+  <si>
+    <t>Proper page alignment should always be maintained.</t>
+  </si>
+  <si>
+    <t>An issue with alignment breakdown has been identified.</t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/1b388bd9-a49f-4563-8345-8671539786f6</t>
+  </si>
+  <si>
+    <t>ai_narrative</t>
+  </si>
+  <si>
+    <t>Alignment issue on AI narrative page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative </t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/8a75fd38-40a6-4076-9a75-206f6dcc8402</t>
+  </si>
+  <si>
+    <t>AI narration modifies data.</t>
+  </si>
+  <si>
+    <t>The Vietnam War, which took place from 1955 to 1975, should have its data accurately updated and presented in a narrative form.</t>
+  </si>
+  <si>
+    <t>Neck and shoulder conditions occurred during the Vietnam War timeline, which ended in 1975, while leg and arm conditions happened after 1975 and were not related to the Vietnam War period.</t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/cdc6f837-e92a-4ab0-80e7-06bb578c52c5</t>
+  </si>
+  <si>
+    <t>Accurate health issues should be displayed or narrated in an AI narrative.</t>
+  </si>
+  <si>
+    <t>PTSD was not selected as a health issue, but it was mentioned in the AI narrative.</t>
+  </si>
+  <si>
+    <t>https://jam.dev/c/562a0661-00db-4406-9b80-91a1e3b22baa</t>
   </si>
 </sst>
 </file>
@@ -2059,7 +2159,7 @@
       </c>
       <c r="E3" s="11">
         <f>COUNTIF('Tahsin (Mobile Phone User)'!K14:K1005, "High") + COUNTIF(Fahad!K9:K1002, "High") + COUNTIF('Tahsin (PC User)'!K14:K1009, "High")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="3"/>
@@ -2096,7 +2196,7 @@
       </c>
       <c r="E4" s="11">
         <f>COUNTIF('Tahsin (Mobile Phone User)'!K14:K1006, "Medium") + COUNTIF(Fahad!K9:K1003, "Medium") + COUNTIF('Tahsin (PC User)'!K14:K1009, "Medium")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="3"/>
@@ -2131,7 +2231,7 @@
       </c>
       <c r="E5" s="11">
         <f>COUNTIF('Tahsin (Mobile Phone User)'!K14:K1007, "Low") + COUNTIF(Fahad!K9:K1004, "Low") + COUNTIF('Tahsin (PC User)'!K14:K1009, "Low")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="3"/>
@@ -2196,7 +2296,7 @@
       </c>
       <c r="E7" s="15">
         <f>SUM(E3:E5)</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -2229,7 +2329,7 @@
       </c>
       <c r="E8" s="15">
         <f>COUNTIF(N12:N1004, "Solved")</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -2592,46 +2692,42 @@
         <v>33</v>
       </c>
       <c r="B15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"
-Mobile Device
-Landing Page (Light Mode)")</f>
-        <v>
-Mobile Device
-Landing Page (Light Mode)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
       </c>
       <c r="C15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Calculator")</f>
-        <v>Calculator</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ai_narrative")</f>
+        <v>ai_narrative</v>
       </c>
       <c r="D15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that both disability type and percentage selections are highlighted consistently")</f>
-        <v>Verify that both disability type and percentage selections are highlighted consistently</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alignment issue on AI narrative page.")</f>
+        <v>Alignment issue on AI narrative page.</v>
       </c>
       <c r="E15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on the Physical Disability Calculator section on a mobile device")</f>
-        <v>User is on the Physical Disability Calculator section on a mobile device</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Navigate to the Physical Disability Calculator 
-3. Select a physical disability type 
-4. Select a percentage value")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Navigate to the Physical Disability Calculator 
-3. Select a physical disability type 
-4. Select a percentage value</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative </v>
       </c>
       <c r="G15" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
       </c>
       <c r="H15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Both selected disability type and selected percentage should be visually highlighted to indicate selection")</f>
-        <v>Both selected disability type and selected percentage should be visually highlighted to indicate selection</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Proper page alignment should always be maintained.")</f>
+        <v>Proper page alignment should always be maintained.</v>
       </c>
       <c r="I15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Only the disability type is highlighted; percentage selection has no visual indication")</f>
-        <v>Only the disability type is highlighted; percentage selection has no visual indication</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An issue with alignment breakdown has been identified.")</f>
+        <v>An issue with alignment breakdown has been identified.</v>
       </c>
       <c r="J15" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -2642,13 +2738,10 @@
         <v>Low</v>
       </c>
       <c r="L15" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/a7618719-d759-477c-8f92-3bc19a277051")</f>
-        <v>https://jam.dev/c/a7618719-d759-477c-8f92-3bc19a277051</v>
-      </c>
-      <c r="M15" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Apply consistent styling to percentage selection (e.g., background color or border) to visually confirm selection")</f>
-        <v>Apply consistent styling to percentage selection (e.g., background color or border) to visually confirm selection</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/8a75fd38-40a6-4076-9a75-206f6dcc8402")</f>
+        <v>https://jam.dev/c/8a75fd38-40a6-4076-9a75-206f6dcc8402</v>
+      </c>
+      <c r="M15" s="15"/>
       <c r="N15" s="13" t="s">
         <v>30</v>
       </c>
@@ -2670,47 +2763,54 @@
         <v>34</v>
       </c>
       <c r="B16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
       </c>
       <c r="C16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
-        <v>Contact us</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ai_narrative")</f>
+        <v>ai_narrative</v>
       </c>
       <c r="D16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Input box design and fields changed based on client requirements.")</f>
-        <v>Input box design and fields changed based on client requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AI narration modifies data.")</f>
+        <v>AI narration modifies data.</v>
       </c>
       <c r="E16" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F16" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2.Scroll down to contact us section")</f>
-        <v>1. Open VALR
-2.Scroll down to contact us section</v>
-      </c>
-      <c r="G16" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative </v>
+      </c>
+      <c r="G16" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
+      </c>
       <c r="H16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us form should as same as client requirement")</f>
-        <v>Contact us form should as same as client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The Vietnam War, which took place from 1955 to 1975, should have its data accurately updated and presented in a narrative form.")</f>
+        <v>The Vietnam War, which took place from 1955 to 1975, should have its data accurately updated and presented in a narrative form.</v>
       </c>
       <c r="I16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A phone box was added that was not part of the client requirements, and the layout differs from what was specified in the requirements.")</f>
-        <v>A phone box was added that was not part of the client requirements, and the layout differs from what was specified in the requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Neck and shoulder conditions occurred during the Vietnam War timeline, which ended in 1975, while leg and arm conditions happened after 1975 and were not related to the Vietnam War period.")</f>
+        <v>Neck and shoulder conditions occurred during the Vietnam War timeline, which ended in 1975, while leg and arm conditions happened after 1975 and were not related to the Vietnam War period.</v>
       </c>
       <c r="J16" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K16" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L16" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/274e93b2-8c31-4a53-84c8-0721d951a951")</f>
-        <v>https://jam.dev/c/274e93b2-8c31-4a53-84c8-0721d951a951</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/cdc6f837-e92a-4ab0-80e7-06bb578c52c5")</f>
+        <v>https://jam.dev/c/cdc6f837-e92a-4ab0-80e7-06bb578c52c5</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="13" t="s">
@@ -2734,47 +2834,54 @@
         <v>35</v>
       </c>
       <c r="B17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
       </c>
       <c r="C17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
-        <v>Contact us</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ai_narrative")</f>
+        <v>ai_narrative</v>
       </c>
       <c r="D17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Image corners are not the same as in Figma.")</f>
-        <v>Image corners are not the same as in Figma.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AI narration modifies data.")</f>
+        <v>AI narration modifies data.</v>
       </c>
       <c r="E17" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F17" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2.Scroll down to contact us section")</f>
-        <v>1. Open VALR
-2.Scroll down to contact us section</v>
-      </c>
-      <c r="G17" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and goto AI Narrative </v>
+      </c>
+      <c r="G17" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
+      </c>
       <c r="H17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Based on the Figma design, the image corners should be angled.")</f>
-        <v>Based on the Figma design, the image corners should be angled.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Accurate health issues should be displayed or narrated in an AI narrative.")</f>
+        <v>Accurate health issues should be displayed or narrated in an AI narrative.</v>
       </c>
       <c r="I17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Two curved and two angled corners are shown, which is asymmetrical and does not align with the client's requirements.")</f>
-        <v>Two curved and two angled corners are shown, which is asymmetrical and does not align with the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PTSD was not selected as a health issue, but it was mentioned in the AI narrative.")</f>
+        <v>PTSD was not selected as a health issue, but it was mentioned in the AI narrative.</v>
       </c>
       <c r="J17" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K17" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L17" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/bf359085-b448-4604-822f-bcc5a7ae50d4")</f>
-        <v>https://jam.dev/c/bf359085-b448-4604-822f-bcc5a7ae50d4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/562a0661-00db-4406-9b80-91a1e3b22baa")</f>
+        <v>https://jam.dev/c/562a0661-00db-4406-9b80-91a1e3b22baa</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="13" t="s">
@@ -2798,56 +2905,63 @@
         <v>36</v>
       </c>
       <c r="B18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"
+Mobile Device
+Landing Page (Light Mode)")</f>
+        <v>
+Mobile Device
+Landing Page (Light Mode)</v>
       </c>
       <c r="C18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
-        <v>Contact us</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Calculator")</f>
+        <v>Calculator</v>
       </c>
       <c r="D18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Handle incorrect input in input fields.")</f>
-        <v>Handle incorrect input in input fields.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that both disability type and percentage selections are highlighted consistently")</f>
+        <v>Verify that both disability type and percentage selections are highlighted consistently</v>
       </c>
       <c r="E18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on the Physical Disability Calculator section on a mobile device")</f>
+        <v>User is on the Physical Disability Calculator section on a mobile device</v>
       </c>
       <c r="F18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
-2. Sign in using valid credentials.
-3. Goto Contact Us ")</f>
-        <v>1. Open VALR.  
-2. Sign in using valid credentials.
-3. Goto Contact Us </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Navigate to the Physical Disability Calculator 
+3. Select a physical disability type 
+4. Select a percentage value")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Navigate to the Physical Disability Calculator 
+3. Select a physical disability type 
+4. Select a percentage value</v>
       </c>
       <c r="G18" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The form should be designed to accept specific data types, such as numbers in the phone input field and characters in the name fields.")</f>
-        <v>The form should be designed to accept specific data types, such as numbers in the phone input field and characters in the name fields.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Both selected disability type and selected percentage should be visually highlighted to indicate selection")</f>
+        <v>Both selected disability type and selected percentage should be visually highlighted to indicate selection</v>
       </c>
       <c r="I18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Phone number fields accept character input, and name fields allow numeric values, leading to an input validation mismatch.")</f>
-        <v>Phone number fields accept character input, and name fields allow numeric values, leading to an input validation mismatch.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Only the disability type is highlighted; percentage selection has no visual indication")</f>
+        <v>Only the disability type is highlighted; percentage selection has no visual indication</v>
       </c>
       <c r="J18" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K18" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L18" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/5aaba718-3a6c-4865-9743-0b788bbf1907")</f>
-        <v>https://jam.dev/c/5aaba718-3a6c-4865-9743-0b788bbf1907</v>
-      </c>
-      <c r="M18" s="15"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/a7618719-d759-477c-8f92-3bc19a277051")</f>
+        <v>https://jam.dev/c/a7618719-d759-477c-8f92-3bc19a277051</v>
+      </c>
+      <c r="M18" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Apply consistent styling to percentage selection (e.g., background color or border) to visually confirm selection")</f>
+        <v>Apply consistent styling to percentage selection (e.g., background color or border) to visually confirm selection</v>
+      </c>
       <c r="N18" s="13" t="s">
         <v>30</v>
       </c>
@@ -2873,12 +2987,12 @@
         <v>Home</v>
       </c>
       <c r="C19" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FAQ")</f>
-        <v>FAQ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
+        <v>Contact us</v>
       </c>
       <c r="D19" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FQA layout update using Figma design.")</f>
-        <v>FQA layout update using Figma design.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Input box design and fields changed based on client requirements.")</f>
+        <v>Input box design and fields changed based on client requirements.</v>
       </c>
       <c r="E19" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -2886,30 +3000,30 @@
       </c>
       <c r="F19" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to FQA Section")</f>
+2.Scroll down to contact us section")</f>
         <v>1. Open VALR
-2. Scroll down to FQA Section</v>
+2.Scroll down to contact us section</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Content layout should be similar to the client's requirements.")</f>
-        <v>Content layout should be similar to the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us form should as same as client requirement")</f>
+        <v>Contact us form should as same as client requirement</v>
       </c>
       <c r="I19" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different layout design has been observed in the FAQ section.")</f>
-        <v>A different layout design has been observed in the FAQ section.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A phone box was added that was not part of the client requirements, and the layout differs from what was specified in the requirements.")</f>
+        <v>A phone box was added that was not part of the client requirements, and the layout differs from what was specified in the requirements.</v>
       </c>
       <c r="J19" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K19" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L19" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1a16a164-3926-488d-b4c5-a8eb3a4a269d")</f>
-        <v>https://jam.dev/c/1a16a164-3926-488d-b4c5-a8eb3a4a269d</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/274e93b2-8c31-4a53-84c8-0721d951a951")</f>
+        <v>https://jam.dev/c/274e93b2-8c31-4a53-84c8-0721d951a951</v>
       </c>
       <c r="M19" s="15"/>
       <c r="N19" s="13" t="s">
@@ -2937,12 +3051,12 @@
         <v>Home</v>
       </c>
       <c r="C20" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Footer")</f>
-        <v>Footer</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
+        <v>Contact us</v>
       </c>
       <c r="D20" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update the footer message as per the design and include a social media link that is not connected to VALR's social media accounts.")</f>
-        <v>Update the footer message as per the design and include a social media link that is not connected to VALR's social media accounts.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Image corners are not the same as in Figma.")</f>
+        <v>Image corners are not the same as in Figma.</v>
       </c>
       <c r="E20" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -2956,24 +3070,24 @@
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The footer section details and alignment should match the client's requirements.")</f>
-        <v>The footer section details and alignment should match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Based on the Figma design, the image corners should be angled.")</f>
+        <v>Based on the Figma design, the image corners should be angled.</v>
       </c>
       <c r="I20" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The layout design differs from the client's requirements, and while social media is beneficial, the link connected to VALR's official social media is inaccurate.")</f>
-        <v>The layout design differs from the client's requirements, and while social media is beneficial, the link connected to VALR's official social media is inaccurate.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Two curved and two angled corners are shown, which is asymmetrical and does not align with the client's requirements.")</f>
+        <v>Two curved and two angled corners are shown, which is asymmetrical and does not align with the client's requirements.</v>
       </c>
       <c r="J20" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K20" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L20" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/c0b840df-8d99-4bf8-ba90-99631091e4ee")</f>
-        <v>https://jam.dev/c/c0b840df-8d99-4bf8-ba90-99631091e4ee</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/bf359085-b448-4604-822f-bcc5a7ae50d4")</f>
+        <v>https://jam.dev/c/bf359085-b448-4604-822f-bcc5a7ae50d4</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="13" t="s">
@@ -2997,61 +3111,58 @@
         <v>39</v>
       </c>
       <c r="B21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC  (Brouser Dark Mode)
-Landing Page")</f>
-        <v>PC  (Brouser Dark Mode)
-Landing Page</v>
-      </c>
-      <c r="C21" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
+      <c r="C21" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Contact us")</f>
+        <v>Contact us</v>
+      </c>
       <c r="D21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage paragraph text is readable over dark background")</f>
-        <v>Verify that homepage paragraph text is readable over dark background</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Handle incorrect input in input fields.")</f>
+        <v>Handle incorrect input in input fields.</v>
       </c>
       <c r="E21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a PC device and on the homepage")</f>
-        <v>User is on a PC device and on the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the section with the text: ""Tired of delays, paperwork, and confusion? VALR makes filing your VA claim fast and stress-free..."" 
-3. Observe the text color against the background")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the section with the text: "Tired of delays, paperwork, and confusion? VALR makes filing your VA claim fast and stress-free..." 
-3. Observe the text color against the background</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Goto Contact Us ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Goto Contact Us </v>
       </c>
       <c r="G21" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
       </c>
       <c r="H21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text should be easily readable with enough contrast even in dark-themed sections")</f>
-        <v>Text should be easily readable with enough contrast even in dark-themed sections</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The form should be designed to accept specific data types, such as numbers in the phone input field and characters in the name fields.")</f>
+        <v>The form should be designed to accept specific data types, such as numbers in the phone input field and characters in the name fields.</v>
       </c>
       <c r="I21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text appears dark over a dark background, making it difficult to read")</f>
-        <v>Text appears dark over a dark background, making it difficult to read</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Phone number fields accept character input, and name fields allow numeric values, leading to an input validation mismatch.")</f>
+        <v>Phone number fields accept character input, and name fields allow numeric values, leading to an input validation mismatch.</v>
       </c>
       <c r="J21" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L21" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/215db53b-812b-4c4e-93a7-03b48bf2ff67")</f>
-        <v>https://jam.dev/c/215db53b-812b-4c4e-93a7-03b48bf2ff67</v>
-      </c>
-      <c r="M21" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update text color to a lighter shade or adjust background opacity to ensure sufficient contrast and readability")</f>
-        <v>Update text color to a lighter shade or adjust background opacity to ensure sufficient contrast and readability</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/5aaba718-3a6c-4865-9743-0b788bbf1907")</f>
+        <v>https://jam.dev/c/5aaba718-3a6c-4865-9743-0b788bbf1907</v>
+      </c>
+      <c r="M21" s="15"/>
       <c r="N21" s="13" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
@@ -3068,45 +3179,38 @@
     </row>
     <row r="22">
       <c r="A22" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
-PC")</f>
-        <v>Landing Page 
-PC</v>
-      </c>
-      <c r="C22" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
+      <c r="C22" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FAQ")</f>
+        <v>FAQ</v>
+      </c>
       <c r="D22" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
-        <v>Verify that homepage UI is correct </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FQA layout update using Figma design.")</f>
+        <v>FQA layout update using Figma design.</v>
       </c>
       <c r="E22" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
-        <v>User is on  the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Top of the home page 
-3. Observe the layout")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Top of the home page 
-3. Observe the layout</v>
-      </c>
-      <c r="G22" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2. Scroll down to FQA Section")</f>
+        <v>1. Open VALR
+2. Scroll down to FQA Section</v>
+      </c>
+      <c r="G22" s="20"/>
       <c r="H22" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
-        <v>UI should match with the client requirements</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Content layout should be similar to the client's requirements.")</f>
+        <v>Content layout should be similar to the client's requirements.</v>
       </c>
       <c r="I22" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
-        <v>Not matched with the client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different layout design has been observed in the FAQ section.")</f>
+        <v>A different layout design has been observed in the FAQ section.</v>
       </c>
       <c r="J22" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3117,8 +3221,8 @@
         <v>Low</v>
       </c>
       <c r="L22" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1f06cefb-bd1f-42b9-9bc5-736604e888e0")</f>
-        <v>https://jam.dev/c/1f06cefb-bd1f-42b9-9bc5-736604e888e0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1a16a164-3926-488d-b4c5-a8eb3a4a269d")</f>
+        <v>https://jam.dev/c/1a16a164-3926-488d-b4c5-a8eb3a4a269d</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="13" t="s">
@@ -3139,57 +3243,50 @@
     </row>
     <row r="23">
       <c r="A23" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
-PC")</f>
-        <v>Landing Page 
-PC</v>
-      </c>
-      <c r="C23" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
+      <c r="C23" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Footer")</f>
+        <v>Footer</v>
+      </c>
       <c r="D23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
-        <v>Verify that homepage UI is correct </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update the footer message as per the design and include a social media link that is not connected to VALR's social media accounts.")</f>
+        <v>Update the footer message as per the design and include a social media link that is not connected to VALR's social media accounts.</v>
       </c>
       <c r="E23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
-        <v>User is on  the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the get in touch today section 
-3. Observe the layout")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the get in touch today section 
-3. Observe the layout</v>
-      </c>
-      <c r="G23" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2.Scroll down to contact us section")</f>
+        <v>1. Open VALR
+2.Scroll down to contact us section</v>
+      </c>
+      <c r="G23" s="20"/>
       <c r="H23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
-        <v>UI should match with the client requirements</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The footer section details and alignment should match the client's requirements.")</f>
+        <v>The footer section details and alignment should match the client's requirements.</v>
       </c>
       <c r="I23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
-        <v>Not matched with the client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The layout design differs from the client's requirements, and while social media is beneficial, the link connected to VALR's official social media is inaccurate.")</f>
+        <v>The layout design differs from the client's requirements, and while social media is beneficial, the link connected to VALR's official social media is inaccurate.</v>
       </c>
       <c r="J23" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K23" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L23" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/2968f160-9630-4c6f-bba9-5b0e76c9663d")</f>
-        <v>https://jam.dev/c/2968f160-9630-4c6f-bba9-5b0e76c9663d</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/c0b840df-8d99-4bf8-ba90-99631091e4ee")</f>
+        <v>https://jam.dev/c/c0b840df-8d99-4bf8-ba90-99631091e4ee</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="13" t="s">
@@ -3210,57 +3307,57 @@
     </row>
     <row r="24">
       <c r="A24" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
-PC")</f>
-        <v>Landing Page 
-PC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
       </c>
       <c r="C24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"gulf_war_location")</f>
+        <v>gulf_war_location</v>
       </c>
       <c r="D24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
-        <v>Verify that homepage UI is correct </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Missing war location in chart")</f>
+        <v>Missing war location in chart</v>
       </c>
       <c r="E24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
-        <v>User is on  the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the Frequently Asked Questions section 
-3. Observe the layout")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the Frequently Asked Questions section 
-3. Observe the layout</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 9th steps ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 9th steps </v>
       </c>
       <c r="G24" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
       </c>
       <c r="H24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
-        <v>UI should match with the client requirements</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Accurate locations of U.S. involvement in wars need to be displayed for veterans to choose their fighting regions.")</f>
+        <v>Accurate locations of U.S. involvement in wars need to be displayed for veterans to choose their fighting regions.</v>
       </c>
       <c r="I24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
-        <v>Not matched with the client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The United States has conflicts with various countries, but Gulf War-related risk locations are the only ones highlighted, potentially causing veterans to miss out on VA benefits.")</f>
+        <v>The United States has conflicts with various countries, but Gulf War-related risk locations are the only ones highlighted, potentially causing veterans to miss out on VA benefits.</v>
       </c>
       <c r="J24" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K24" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L24" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/debe4d04-3b2c-47d2-accd-2810beda0e9b")</f>
-        <v>https://jam.dev/c/debe4d04-3b2c-47d2-accd-2810beda0e9b</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/0a02aaf8-8e4e-407a-9ead-21cf454d357e")</f>
+        <v>https://jam.dev/c/0a02aaf8-8e4e-407a-9ead-21cf454d357e</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="13" t="s">
@@ -3281,45 +3378,45 @@
     </row>
     <row r="25">
       <c r="A25" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
-PC")</f>
-        <v>Landing Page 
-PC</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC  (Brouser Dark Mode)
+Landing Page")</f>
+        <v>PC  (Brouser Dark Mode)
+Landing Page</v>
       </c>
       <c r="C25" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="D25" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
-        <v>Verify that homepage UI is correct </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage paragraph text is readable over dark background")</f>
+        <v>Verify that homepage paragraph text is readable over dark background</v>
       </c>
       <c r="E25" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
-        <v>User is on  the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a PC device and on the homepage")</f>
+        <v>User is on a PC device and on the homepage</v>
       </c>
       <c r="F25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the THROUGH EDUCATION section 
-3. Observe the layout")</f>
+2. Scroll to the section with the text: ""Tired of delays, paperwork, and confusion? VALR makes filing your VA claim fast and stress-free..."" 
+3. Observe the text color against the background")</f>
         <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll to the THROUGH EDUCATION section 
-3. Observe the layout</v>
+2. Scroll to the section with the text: "Tired of delays, paperwork, and confusion? VALR makes filing your VA claim fast and stress-free..." 
+3. Observe the text color against the background</v>
       </c>
       <c r="G25" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="H25" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
-        <v>UI should match with the client requirements</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text should be easily readable with enough contrast even in dark-themed sections")</f>
+        <v>Text should be easily readable with enough contrast even in dark-themed sections</v>
       </c>
       <c r="I25" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
-        <v>Not matched with the client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text appears dark over a dark background, making it difficult to read")</f>
+        <v>Text appears dark over a dark background, making it difficult to read</v>
       </c>
       <c r="J25" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3330,10 +3427,13 @@
         <v>Medium</v>
       </c>
       <c r="L25" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/6c2f0795-5a52-4b4c-9b68-f30e6b436e7b")</f>
-        <v>https://jam.dev/c/6c2f0795-5a52-4b4c-9b68-f30e6b436e7b</v>
-      </c>
-      <c r="M25" s="15"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/215db53b-812b-4c4e-93a7-03b48bf2ff67")</f>
+        <v>https://jam.dev/c/215db53b-812b-4c4e-93a7-03b48bf2ff67</v>
+      </c>
+      <c r="M25" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update text color to a lighter shade or adjust background opacity to ensure sufficient contrast and readability")</f>
+        <v>Update text color to a lighter shade or adjust background opacity to ensure sufficient contrast and readability</v>
+      </c>
       <c r="N25" s="13" t="s">
         <v>30</v>
       </c>
@@ -3352,45 +3452,45 @@
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC (Brouser Dark + light Mode)
-Landing Page")</f>
-        <v>PC (Brouser Dark + light Mode)
-Landing Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
+PC")</f>
+        <v>Landing Page 
+PC</v>
       </c>
       <c r="C26" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="D26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that there is no unnecessary blank space above the Services section")</f>
-        <v>Verify that there is no unnecessary blank space above the Services section</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
+        <v>Verify that homepage UI is correct </v>
       </c>
       <c r="E26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a PC device and on the homepage")</f>
-        <v>User is on a PC device and on the homepage</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
+        <v>User is on  the homepage</v>
       </c>
       <c r="F26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll down to the Services section 
-3. Observe the spacing above the section")</f>
+2. Top of the home page 
+3. Observe the layout")</f>
         <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Scroll down to the Services section 
-3. Observe the spacing above the section</v>
+2. Top of the home page 
+3. Observe the layout</v>
       </c>
       <c r="G26" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="H26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Spacing above Services section should be consistent and free of large empty gaps")</f>
-        <v>Spacing above Services section should be consistent and free of large empty gaps</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
+        <v>UI should match with the client requirements</v>
       </c>
       <c r="I26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"There is an unusual blank space above the Services section")</f>
-        <v>There is an unusual blank space above the Services section</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
+        <v>Not matched with the client requirement</v>
       </c>
       <c r="J26" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3401,13 +3501,10 @@
         <v>Low</v>
       </c>
       <c r="L26" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/72bb2f2e-40cc-41cd-a0e6-9dac05197357")</f>
-        <v>https://jam.dev/c/72bb2f2e-40cc-41cd-a0e6-9dac05197357</v>
-      </c>
-      <c r="M26" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Review and adjust CSS layout/margins to eliminate unnecessary whitespace and maintain visual consistency")</f>
-        <v>Review and adjust CSS layout/margins to eliminate unnecessary whitespace and maintain visual consistency</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1f06cefb-bd1f-42b9-9bc5-736604e888e0")</f>
+        <v>https://jam.dev/c/1f06cefb-bd1f-42b9-9bc5-736604e888e0</v>
+      </c>
+      <c r="M26" s="15"/>
       <c r="N26" s="13" t="s">
         <v>30</v>
       </c>
@@ -3426,41 +3523,45 @@
     </row>
     <row r="27">
       <c r="A27" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
+PC")</f>
+        <v>Landing Page 
+PC</v>
+      </c>
+      <c r="C27" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
-      <c r="C27" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home page")</f>
-        <v>Home page</v>
-      </c>
       <c r="D27" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Profile icon use in VAFORM section")</f>
-        <v>Profile icon use in VAFORM section</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
+        <v>Verify that homepage UI is correct </v>
       </c>
       <c r="E27" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
+        <v>User is on  the homepage</v>
       </c>
       <c r="F27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  2. Sign in using valid credentials.")</f>
-        <v>1. Open VALR.  2. Sign in using valid credentials.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the get in touch today section 
+3. Observe the layout")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the get in touch today section 
+3. Observe the layout</v>
       </c>
       <c r="G27" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H27" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An icon should make sense.")</f>
-        <v>An icon should make sense.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
+        <v>UI should match with the client requirements</v>
       </c>
       <c r="I27" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VAFORM is documented in the Profile icon")</f>
-        <v>VAFORM is documented in the Profile icon</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
+        <v>Not matched with the client requirement</v>
       </c>
       <c r="J27" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3471,8 +3572,8 @@
         <v>Medium</v>
       </c>
       <c r="L27" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/19b28142-f8ca-4af4-90c1-7dd7e98e9fc6")</f>
-        <v>https://jam.dev/c/19b28142-f8ca-4af4-90c1-7dd7e98e9fc6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/2968f160-9630-4c6f-bba9-5b0e76c9663d")</f>
+        <v>https://jam.dev/c/2968f160-9630-4c6f-bba9-5b0e76c9663d</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="13" t="s">
@@ -3493,55 +3594,57 @@
     </row>
     <row r="28">
       <c r="A28" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
+PC")</f>
+        <v>Landing Page 
+PC</v>
+      </c>
+      <c r="C28" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
-      <c r="C28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
-        <v>Home Page</v>
-      </c>
       <c r="D28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different video content is displayed when users log in to the system.")</f>
-        <v>Different video content is displayed when users log in to the system.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
+        <v>Verify that homepage UI is correct </v>
       </c>
       <c r="E28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
+        <v>User is on  the homepage</v>
       </c>
       <c r="F28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
-2. Sign in using valid credentials.")</f>
-        <v>1. Open VALR.  
-2. Sign in using valid credentials.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the Frequently Asked Questions section 
+3. Observe the layout")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the Frequently Asked Questions section 
+3. Observe the layout</v>
       </c>
       <c r="G28" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video content should remain consistent on the page for user information.")</f>
-        <v>Video content should remain consistent on the page for user information.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
+        <v>UI should match with the client requirements</v>
       </c>
       <c r="I28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different video is displayed, which can lead to misinformation issues.")</f>
-        <v>A different video is displayed, which can lead to misinformation issues.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
+        <v>Not matched with the client requirement</v>
       </c>
       <c r="J28" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K28" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L28" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/5c75a6c3-df26-4cb1-abce-bba7051c7aea")</f>
-        <v>https://jam.dev/c/5c75a6c3-df26-4cb1-abce-bba7051c7aea</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/debe4d04-3b2c-47d2-accd-2810beda0e9b")</f>
+        <v>https://jam.dev/c/debe4d04-3b2c-47d2-accd-2810beda0e9b</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="13" t="s">
@@ -3549,7 +3652,7 @@
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
@@ -3564,43 +3667,45 @@
     </row>
     <row r="29">
       <c r="A29" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page 
+PC")</f>
+        <v>Landing Page 
+PC</v>
+      </c>
+      <c r="C29" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
-      <c r="C29" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
-        <v>Home Page</v>
-      </c>
       <c r="D29" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video lacks shading, and the corners are not symmetrical.")</f>
-        <v>The video lacks shading, and the corners are not symmetrical.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that homepage UI is correct ")</f>
+        <v>Verify that homepage UI is correct </v>
       </c>
       <c r="E29" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on  the homepage")</f>
+        <v>User is on  the homepage</v>
       </c>
       <c r="F29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
-2. Sign in using valid credentials.")</f>
-        <v>1. Open VALR.  
-2. Sign in using valid credentials.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the THROUGH EDUCATION section 
+3. Observe the layout")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll to the THROUGH EDUCATION section 
+3. Observe the layout</v>
       </c>
       <c r="G29" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H29" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Proper design should align with the requirements.")</f>
-        <v>Proper design should align with the requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UI should match with the client requirements")</f>
+        <v>UI should match with the client requirements</v>
       </c>
       <c r="I29" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different designs and web apps are displayed.")</f>
-        <v>Different designs and web apps are displayed.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Not matched with the client requirement")</f>
+        <v>Not matched with the client requirement</v>
       </c>
       <c r="J29" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3611,8 +3716,8 @@
         <v>Medium</v>
       </c>
       <c r="L29" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/74a4e051-7867-4d6a-ada6-a0130384d075")</f>
-        <v>https://jam.dev/c/74a4e051-7867-4d6a-ada6-a0130384d075</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/6c2f0795-5a52-4b4c-9b68-f30e6b436e7b")</f>
+        <v>https://jam.dev/c/6c2f0795-5a52-4b4c-9b68-f30e6b436e7b</v>
       </c>
       <c r="M29" s="15"/>
       <c r="N29" s="13" t="s">
@@ -3620,7 +3725,7 @@
       </c>
       <c r="O29" s="5"/>
       <c r="P29" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
@@ -3635,57 +3740,62 @@
     </row>
     <row r="30">
       <c r="A30" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC (Brouser Dark + light Mode)
+Landing Page")</f>
+        <v>PC (Brouser Dark + light Mode)
+Landing Page</v>
+      </c>
+      <c r="C30" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
-      <c r="C30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
-        <v>Home Page</v>
-      </c>
       <c r="D30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been observed.")</f>
-        <v>An alignment issue has been observed.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that there is no unnecessary blank space above the Services section")</f>
+        <v>Verify that there is no unnecessary blank space above the Services section</v>
       </c>
       <c r="E30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a PC device and on the homepage")</f>
+        <v>User is on a PC device and on the homepage</v>
       </c>
       <c r="F30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
-2. Sign in using valid credentials.")</f>
-        <v>1. Open VALR.  
-2. Sign in using valid credentials.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll down to the Services section 
+3. Observe the spacing above the section")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Scroll down to the Services section 
+3. Observe the spacing above the section</v>
       </c>
       <c r="G30" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The alignment should match the client's requirements.")</f>
-        <v>The alignment should match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Spacing above Services section should be consistent and free of large empty gaps")</f>
+        <v>Spacing above Services section should be consistent and free of large empty gaps</v>
       </c>
       <c r="I30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been detected, which can sometimes result in user dissatisfaction.")</f>
-        <v>An alignment issue has been detected, which can sometimes result in user dissatisfaction.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"There is an unusual blank space above the Services section")</f>
+        <v>There is an unusual blank space above the Services section</v>
       </c>
       <c r="J30" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K30" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L30" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/584df2cc-d534-4559-9c20-0c74bb4326e1")</f>
-        <v>https://jam.dev/c/584df2cc-d534-4559-9c20-0c74bb4326e1</v>
-      </c>
-      <c r="M30" s="15"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/72bb2f2e-40cc-41cd-a0e6-9dac05197357")</f>
+        <v>https://jam.dev/c/72bb2f2e-40cc-41cd-a0e6-9dac05197357</v>
+      </c>
+      <c r="M30" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Review and adjust CSS layout/margins to eliminate unnecessary whitespace and maintain visual consistency")</f>
+        <v>Review and adjust CSS layout/margins to eliminate unnecessary whitespace and maintain visual consistency</v>
+      </c>
       <c r="N30" s="13" t="s">
         <v>30</v>
       </c>
@@ -3704,29 +3814,27 @@
     </row>
     <row r="31">
       <c r="A31" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="C31" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
-        <v>Home Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home page")</f>
+        <v>Home page</v>
       </c>
       <c r="D31" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The claim layout differs from the client's requirements.")</f>
-        <v>The claim layout differs from the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Profile icon use in VAFORM section")</f>
+        <v>Profile icon use in VAFORM section</v>
       </c>
       <c r="E31" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F31" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
-2. Sign in using valid credentials.")</f>
-        <v>1. Open VALR.  
-2. Sign in using valid credentials.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  2. Sign in using valid credentials.")</f>
+        <v>1. Open VALR.  2. Sign in using valid credentials.</v>
       </c>
       <c r="G31" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
@@ -3735,14 +3843,12 @@
 Pass : 12345678</v>
       </c>
       <c r="H31" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The claim page layout should match the client's requirements.")</f>
-        <v>The claim page layout should match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An icon should make sense.")</f>
+        <v>An icon should make sense.</v>
       </c>
       <c r="I31" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different user interface, different image displayed.
-Also video added which was not in design")</f>
-        <v>Different user interface, different image displayed.
-Also video added which was not in design</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VAFORM is documented in the Profile icon")</f>
+        <v>VAFORM is documented in the Profile icon</v>
       </c>
       <c r="J31" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3753,8 +3859,8 @@
         <v>Medium</v>
       </c>
       <c r="L31" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/d49e5e4e-7252-4a2b-b250-63483159d613")</f>
-        <v>https://jam.dev/c/d49e5e4e-7252-4a2b-b250-63483159d613</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/19b28142-f8ca-4af4-90c1-7dd7e98e9fc6")</f>
+        <v>https://jam.dev/c/19b28142-f8ca-4af4-90c1-7dd7e98e9fc6</v>
       </c>
       <c r="M31" s="15"/>
       <c r="N31" s="13" t="s">
@@ -3762,7 +3868,7 @@
       </c>
       <c r="O31" s="5"/>
       <c r="P31" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
@@ -3777,7 +3883,7 @@
     </row>
     <row r="32">
       <c r="A32" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B32" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
@@ -3788,8 +3894,8 @@
         <v>Home Page</v>
       </c>
       <c r="D32" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A line is visible when used in night mode.")</f>
-        <v>A line is visible when used in night mode.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different video content is displayed when users log in to the system.")</f>
+        <v>Different video content is displayed when users log in to the system.</v>
       </c>
       <c r="E32" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -3808,24 +3914,24 @@
 Pass : 12345678</v>
       </c>
       <c r="H32" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The line beneath the icon should not be visible in the web app.")</f>
-        <v>The line beneath the icon should not be visible in the web app.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video content should remain consistent on the page for user information.")</f>
+        <v>Video content should remain consistent on the page for user information.</v>
       </c>
       <c r="I32" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The line beneath the icon is noticeable in night mode.")</f>
-        <v>The line beneath the icon is noticeable in night mode.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different video is displayed, which can lead to misinformation issues.")</f>
+        <v>A different video is displayed, which can lead to misinformation issues.</v>
       </c>
       <c r="J32" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K32" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L32" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/80518c60-dcee-4c92-8179-27abe13342e5")</f>
-        <v>https://jam.dev/c/80518c60-dcee-4c92-8179-27abe13342e5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/5c75a6c3-df26-4cb1-abce-bba7051c7aea")</f>
+        <v>https://jam.dev/c/5c75a6c3-df26-4cb1-abce-bba7051c7aea</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="13" t="s">
@@ -3846,50 +3952,55 @@
     </row>
     <row r="33">
       <c r="A33" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B33" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="C33" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
-        <v>Landing Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
+        <v>Home Page</v>
       </c>
       <c r="D33" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A significant gap has been noticed.")</f>
-        <v>A significant gap has been noticed.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video lacks shading, and the corners are not symmetrical.")</f>
+        <v>The video lacks shading, and the corners are not symmetrical.</v>
       </c>
       <c r="E33" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F33" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to first video")</f>
-        <v>1. Open VALR
-2. Scroll down to first video</v>
-      </c>
-      <c r="G33" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.</v>
+      </c>
+      <c r="G33" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
+      </c>
       <c r="H33" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The gap between contents should be determined user requirements.")</f>
-        <v>The gap between contents should be determined user requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Proper design should align with the requirements.")</f>
+        <v>Proper design should align with the requirements.</v>
       </c>
       <c r="I33" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Noticed a significant gap.")</f>
-        <v>Noticed a significant gap.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different designs and web apps are displayed.")</f>
+        <v>Different designs and web apps are displayed.</v>
       </c>
       <c r="J33" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K33" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L33" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1636caed-a178-46a7-aef8-4afdd970d596")</f>
-        <v>https://jam.dev/c/1636caed-a178-46a7-aef8-4afdd970d596</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/74a4e051-7867-4d6a-ada6-a0130384d075")</f>
+        <v>https://jam.dev/c/74a4e051-7867-4d6a-ada6-a0130384d075</v>
       </c>
       <c r="M33" s="15"/>
       <c r="N33" s="13" t="s">
@@ -3910,38 +4021,43 @@
     </row>
     <row r="34">
       <c r="A34" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="C34" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
-        <v>Landing Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
+        <v>Home Page</v>
       </c>
       <c r="D34" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The landing page is missing a contact option.")</f>
-        <v>The landing page is missing a contact option.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been observed.")</f>
+        <v>An alignment issue has been observed.</v>
       </c>
       <c r="E34" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F34" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to first video")</f>
-        <v>1. Open VALR
-2. Scroll down to first video</v>
-      </c>
-      <c r="G34" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.</v>
+      </c>
+      <c r="G34" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
+      </c>
       <c r="H34" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The contact option should be prominently displayed at the top of user engagement.")</f>
-        <v>The contact option should be prominently displayed at the top of user engagement.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The alignment should match the client's requirements.")</f>
+        <v>The alignment should match the client's requirements.</v>
       </c>
       <c r="I34" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Missing content buttons shows which sometimes lead to user dissatisfaction.")</f>
-        <v>Missing content buttons shows which sometimes lead to user dissatisfaction.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been detected, which can sometimes result in user dissatisfaction.")</f>
+        <v>An alignment issue has been detected, which can sometimes result in user dissatisfaction.</v>
       </c>
       <c r="J34" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -3952,8 +4068,8 @@
         <v>Medium</v>
       </c>
       <c r="L34" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/88966c97-c8c8-4db9-9faa-609432f036a7")</f>
-        <v>https://jam.dev/c/88966c97-c8c8-4db9-9faa-609432f036a7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/584df2cc-d534-4559-9c20-0c74bb4326e1")</f>
+        <v>https://jam.dev/c/584df2cc-d534-4559-9c20-0c74bb4326e1</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="13" t="s">
@@ -3961,7 +4077,7 @@
       </c>
       <c r="O34" s="5"/>
       <c r="P34" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
@@ -3976,50 +4092,57 @@
     </row>
     <row r="35">
       <c r="A35" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="C35" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
-        <v>Landing Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
+        <v>Home Page</v>
       </c>
       <c r="D35" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been identified that does not match the client's requirements.")</f>
-        <v>An alignment issue has been identified that does not match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The claim layout differs from the client's requirements.")</f>
+        <v>The claim layout differs from the client's requirements.</v>
       </c>
       <c r="E35" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F35" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to first video")</f>
-        <v>1. Open VALR
-2. Scroll down to first video</v>
-      </c>
-      <c r="G35" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.</v>
+      </c>
+      <c r="G35" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
+      </c>
       <c r="H35" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alignment should match user requirements to ensure satisfaction.")</f>
-        <v>Alignment should match user requirements to ensure satisfaction.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The claim page layout should match the client's requirements.")</f>
+        <v>The claim page layout should match the client's requirements.</v>
       </c>
       <c r="I35" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue was found that could result in user dissatisfaction.")</f>
-        <v>An alignment issue was found that could result in user dissatisfaction.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Different user interface, different image displayed.
+Also video added which was not in design")</f>
+        <v>Different user interface, different image displayed.
+Also video added which was not in design</v>
       </c>
       <c r="J35" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K35" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L35" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/732f8fb6-55db-42c9-bca1-1d23789db6f5")</f>
-        <v>https://jam.dev/c/732f8fb6-55db-42c9-bca1-1d23789db6f5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/d49e5e4e-7252-4a2b-b250-63483159d613")</f>
+        <v>https://jam.dev/c/d49e5e4e-7252-4a2b-b250-63483159d613</v>
       </c>
       <c r="M35" s="15"/>
       <c r="N35" s="13" t="s">
@@ -4028,7 +4151,7 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
@@ -4042,38 +4165,43 @@
     </row>
     <row r="36">
       <c r="A36" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
         <v>Home</v>
       </c>
       <c r="C36" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
-        <v>Landing Page</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home Page")</f>
+        <v>Home Page</v>
       </c>
       <c r="D36" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The payment section differs from the Figma design.")</f>
-        <v>The payment section differs from the Figma design.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A line is visible when used in night mode.")</f>
+        <v>A line is visible when used in night mode.</v>
       </c>
       <c r="E36" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F36" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to 2nd video")</f>
-        <v>1. Open VALR
-2. Scroll down to 2nd video</v>
-      </c>
-      <c r="G36" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.</v>
+      </c>
+      <c r="G36" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
+      </c>
       <c r="H36" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The layout should match the client's requirements.")</f>
-        <v>The layout should match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The line beneath the icon should not be visible in the web app.")</f>
+        <v>The line beneath the icon should not be visible in the web app.</v>
       </c>
       <c r="I36" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different layout has been observed.")</f>
-        <v>A different layout has been observed.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The line beneath the icon is noticeable in night mode.")</f>
+        <v>The line beneath the icon is noticeable in night mode.</v>
       </c>
       <c r="J36" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4084,8 +4212,8 @@
         <v>Low</v>
       </c>
       <c r="L36" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/e35cc884-0b6e-4d9f-9651-b9b6862d98c9")</f>
-        <v>https://jam.dev/c/e35cc884-0b6e-4d9f-9651-b9b6862d98c9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/80518c60-dcee-4c92-8179-27abe13342e5")</f>
+        <v>https://jam.dev/c/80518c60-dcee-4c92-8179-27abe13342e5</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="13" t="s">
@@ -4093,7 +4221,7 @@
       </c>
       <c r="O36" s="5"/>
       <c r="P36" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
@@ -4108,7 +4236,7 @@
     </row>
     <row r="37">
       <c r="A37" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B37" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
@@ -4119,8 +4247,8 @@
         <v>Landing Page</v>
       </c>
       <c r="D37" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video corner is not the same as other corners.")</f>
-        <v>The video corner is not the same as other corners.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A significant gap has been noticed.")</f>
+        <v>A significant gap has been noticed.</v>
       </c>
       <c r="E37" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4128,30 +4256,30 @@
       </c>
       <c r="F37" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to 2nd video")</f>
+2. Scroll down to first video")</f>
         <v>1. Open VALR
-2. Scroll down to 2nd video</v>
+2. Scroll down to first video</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"All corners of video file should be same ")</f>
-        <v>All corners of video file should be same </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The gap between contents should be determined user requirements.")</f>
+        <v>The gap between contents should be determined user requirements.</v>
       </c>
       <c r="I37" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Three curved corners and one angled corner have been noticed, which makes it asymmetrical.")</f>
-        <v>Three curved corners and one angled corner have been noticed, which makes it asymmetrical.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Noticed a significant gap.")</f>
+        <v>Noticed a significant gap.</v>
       </c>
       <c r="J37" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K37" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
-        <v>Medium</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L37" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/123734b1-0747-4619-8fb8-c1806768912a")</f>
-        <v>https://jam.dev/c/123734b1-0747-4619-8fb8-c1806768912a</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1636caed-a178-46a7-aef8-4afdd970d596")</f>
+        <v>https://jam.dev/c/1636caed-a178-46a7-aef8-4afdd970d596</v>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="13" t="s">
@@ -4172,7 +4300,7 @@
     </row>
     <row r="38">
       <c r="A38" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B38" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
@@ -4183,8 +4311,8 @@
         <v>Landing Page</v>
       </c>
       <c r="D38" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video border shade is not implemented in the web app.")</f>
-        <v>The video border shade is not implemented in the web app.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The landing page is missing a contact option.")</f>
+        <v>The landing page is missing a contact option.</v>
       </c>
       <c r="E38" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4192,18 +4320,18 @@
       </c>
       <c r="F38" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to 2nd video")</f>
+2. Scroll down to first video")</f>
         <v>1. Open VALR
-2. Scroll down to 2nd video</v>
+2. Scroll down to first video</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video shade should match the client's requirements.")</f>
-        <v>The video shade should match the client's requirements.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The contact option should be prominently displayed at the top of user engagement.")</f>
+        <v>The contact option should be prominently displayed at the top of user engagement.</v>
       </c>
       <c r="I38" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A mismatch has been identified between the client's requirements and the developed app.")</f>
-        <v>A mismatch has been identified between the client's requirements and the developed app.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Missing content buttons shows which sometimes lead to user dissatisfaction.")</f>
+        <v>Missing content buttons shows which sometimes lead to user dissatisfaction.</v>
       </c>
       <c r="J38" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4214,8 +4342,8 @@
         <v>Medium</v>
       </c>
       <c r="L38" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/535e6bd5-25ab-4c07-a109-aff9aa5fb5a4")</f>
-        <v>https://jam.dev/c/535e6bd5-25ab-4c07-a109-aff9aa5fb5a4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/88966c97-c8c8-4db9-9faa-609432f036a7")</f>
+        <v>https://jam.dev/c/88966c97-c8c8-4db9-9faa-609432f036a7</v>
       </c>
       <c r="M38" s="15"/>
       <c r="N38" s="13" t="s">
@@ -4223,7 +4351,7 @@
       </c>
       <c r="O38" s="5"/>
       <c r="P38" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
@@ -4238,7 +4366,7 @@
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B39" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
@@ -4249,8 +4377,8 @@
         <v>Landing Page</v>
       </c>
       <c r="D39" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been observed on the landing page.")</f>
-        <v>An alignment issue has been observed on the landing page.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been identified that does not match the client's requirements.")</f>
+        <v>An alignment issue has been identified that does not match the client's requirements.</v>
       </c>
       <c r="E39" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4258,18 +4386,18 @@
       </c>
       <c r="F39" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Scroll down to 2nd video")</f>
+2. Scroll down to first video")</f>
         <v>1. Open VALR
-2. Scroll down to 2nd video</v>
+2. Scroll down to first video</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Allignment should be match with client requirement")</f>
-        <v>Allignment should be match with client requirement</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alignment should match user requirements to ensure satisfaction.")</f>
+        <v>Alignment should match user requirements to ensure satisfaction.</v>
       </c>
       <c r="I39" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A mismatch in alignment with client requirements can result in dissatisfaction.")</f>
-        <v>A mismatch in alignment with client requirements can result in dissatisfaction.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue was found that could result in user dissatisfaction.")</f>
+        <v>An alignment issue was found that could result in user dissatisfaction.</v>
       </c>
       <c r="J39" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4280,8 +4408,8 @@
         <v>Low</v>
       </c>
       <c r="L39" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/eb37c560-e234-415b-95a6-f58bdb594cf8")</f>
-        <v>https://jam.dev/c/eb37c560-e234-415b-95a6-f58bdb594cf8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/732f8fb6-55db-42c9-bca1-1d23789db6f5")</f>
+        <v>https://jam.dev/c/732f8fb6-55db-42c9-bca1-1d23789db6f5</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="13" t="s">
@@ -4302,7 +4430,7 @@
     </row>
     <row r="40">
       <c r="A40" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B40" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
@@ -4313,8 +4441,8 @@
         <v>Landing Page</v>
       </c>
       <c r="D40" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The ""Read More"" option for the content under the banner is missing.")</f>
-        <v>The "Read More" option for the content under the banner is missing.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The payment section differs from the Figma design.")</f>
+        <v>The payment section differs from the Figma design.</v>
       </c>
       <c r="E40" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4328,24 +4456,24 @@
       </c>
       <c r="G40" s="20"/>
       <c r="H40" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The stories banner should include a ""Read More"" option to allow users to view the full history.")</f>
-        <v>The stories banner should include a "Read More" option to allow users to view the full history.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The layout should match the client's requirements.")</f>
+        <v>The layout should match the client's requirements.</v>
       </c>
       <c r="I40" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Missing a ""Read More"" option in a story banner can make users believe the story is fake or created solely for publicity.")</f>
-        <v>Missing a "Read More" option in a story banner can make users believe the story is fake or created solely for publicity.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A different layout has been observed.")</f>
+        <v>A different layout has been observed.</v>
       </c>
       <c r="J40" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K40" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L40" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/421d8638-3a23-4a6c-b704-5362ff64b5dc")</f>
-        <v>https://jam.dev/c/421d8638-3a23-4a6c-b704-5362ff64b5dc</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/e35cc884-0b6e-4d9f-9651-b9b6862d98c9")</f>
+        <v>https://jam.dev/c/e35cc884-0b6e-4d9f-9651-b9b6862d98c9</v>
       </c>
       <c r="M40" s="15"/>
       <c r="N40" s="13" t="s">
@@ -4353,7 +4481,7 @@
       </c>
       <c r="O40" s="5"/>
       <c r="P40" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
@@ -4368,72 +4496,58 @@
     </row>
     <row r="41">
       <c r="A41" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"
-Mobile Device
-Authentication (Dark Mode)")</f>
-        <v>
-Mobile Device
-Authentication (Dark Mode)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
       </c>
       <c r="C41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
-        <v>Login</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
+        <v>Landing Page</v>
       </c>
       <c r="D41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify password field text color in dark mode is clearly visible")</f>
-        <v>Verify password field text color in dark mode is clearly visible</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video corner is not the same as other corners.")</f>
+        <v>The video corner is not the same as other corners.</v>
       </c>
       <c r="E41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User's phone is in dark mode and user is on the login screen of the site")</f>
-        <v>User's phone is in dark mode and user is on the login screen of the site</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Ensure the phone is set to dark mode 
-3. Go to the login screen 
-4. Tap on the password field and type any text")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Ensure the phone is set to dark mode 
-3. Go to the login screen 
-4. Tap on the password field and type any text</v>
-      </c>
-      <c r="G41" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2. Scroll down to 2nd video")</f>
+        <v>1. Open VALR
+2. Scroll down to 2nd video</v>
+      </c>
+      <c r="G41" s="20"/>
       <c r="H41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The typed password should be clearly visible (e.g., light-colored text on dark background)")</f>
-        <v>The typed password should be clearly visible (e.g., light-colored text on dark background)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"All corners of video file should be same ")</f>
+        <v>All corners of video file should be same </v>
       </c>
       <c r="I41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Password text appears black on a dark background, making it hard to see")</f>
-        <v>Password text appears black on a dark background, making it hard to see</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Three curved corners and one angled corner have been noticed, which makes it asymmetrical.")</f>
+        <v>Three curved corners and one angled corner have been noticed, which makes it asymmetrical.</v>
       </c>
       <c r="J41" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
       </c>
       <c r="L41" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/cca7d6de-4a27-4053-8108-3b660e26d30b")</f>
-        <v>https://jam.dev/c/cca7d6de-4a27-4053-8108-3b660e26d30b</v>
-      </c>
-      <c r="M41" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)")</f>
-        <v>Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/123734b1-0747-4619-8fb8-c1806768912a")</f>
+        <v>https://jam.dev/c/123734b1-0747-4619-8fb8-c1806768912a</v>
+      </c>
+      <c r="M41" s="15"/>
       <c r="N41" s="13" t="s">
         <v>30</v>
       </c>
       <c r="O41" s="5"/>
       <c r="P41" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
@@ -4448,19 +4562,19 @@
     </row>
     <row r="42">
       <c r="A42" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B42" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignIn")</f>
-        <v>SignIn</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
       </c>
       <c r="C42" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
-        <v>Login</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
+        <v>Landing Page</v>
       </c>
       <c r="D42" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The password hide icon overlaps when the user attempts to log in or signup")</f>
-        <v>The password hide icon overlaps when the user attempts to log in or signup</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video border shade is not implemented in the web app.")</f>
+        <v>The video border shade is not implemented in the web app.</v>
       </c>
       <c r="E42" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4468,18 +4582,18 @@
       </c>
       <c r="F42" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2.Goto Signin or signup")</f>
+2. Scroll down to 2nd video")</f>
         <v>1. Open VALR
-2.Goto Signin or signup</v>
+2. Scroll down to 2nd video</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The visible and hide option icon for the password should remain consistent.")</f>
-        <v>The visible and hide option icon for the password should remain consistent.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video shade should match the client's requirements.")</f>
+        <v>The video shade should match the client's requirements.</v>
       </c>
       <c r="I42" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The icon overlaps when a user enters input in the password section.")</f>
-        <v>The icon overlaps when a user enters input in the password section.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A mismatch has been identified between the client's requirements and the developed app.")</f>
+        <v>A mismatch has been identified between the client's requirements and the developed app.</v>
       </c>
       <c r="J42" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4490,8 +4604,8 @@
         <v>Medium</v>
       </c>
       <c r="L42" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/fec0b683-8105-450a-a86a-978e8e88eb6f")</f>
-        <v>https://jam.dev/c/fec0b683-8105-450a-a86a-978e8e88eb6f</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/535e6bd5-25ab-4c07-a109-aff9aa5fb5a4")</f>
+        <v>https://jam.dev/c/535e6bd5-25ab-4c07-a109-aff9aa5fb5a4</v>
       </c>
       <c r="M42" s="15"/>
       <c r="N42" s="13" t="s">
@@ -4499,7 +4613,7 @@
       </c>
       <c r="O42" s="5"/>
       <c r="P42" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
@@ -4514,19 +4628,19 @@
     </row>
     <row r="43">
       <c r="A43" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignIn")</f>
-        <v>SignIn</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
       </c>
       <c r="C43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
-        <v>Login</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
+        <v>Landing Page</v>
       </c>
       <c r="D43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"When an unregistered user tries to log in, the prompt doesn't display ""Invalid email and password.""")</f>
-        <v>When an unregistered user tries to log in, the prompt doesn't display "Invalid email and password."</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been observed on the landing page.")</f>
+        <v>An alignment issue has been observed on the landing page.</v>
       </c>
       <c r="E43" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
@@ -4534,30 +4648,30 @@
       </c>
       <c r="F43" s="20" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2.Goto Signin or signup")</f>
+2. Scroll down to 2nd video")</f>
         <v>1. Open VALR
-2.Goto Signin or signup</v>
+2. Scroll down to 2nd video</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"When an unregistered user attempts to log in to the system, the prompt should display a message indicating that the email is not registered in the system.")</f>
-        <v>When an unregistered user attempts to log in to the system, the prompt should display a message indicating that the email is not registered in the system.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Allignment should be match with client requirement")</f>
+        <v>Allignment should be match with client requirement</v>
       </c>
       <c r="I43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The prompt displays ""Something went wrong,"" but it doesn't clarify whether the issue is on the client side or due to a system error.")</f>
-        <v>The prompt displays "Something went wrong," but it doesn't clarify whether the issue is on the client side or due to a system error.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A mismatch in alignment with client requirements can result in dissatisfaction.")</f>
+        <v>A mismatch in alignment with client requirements can result in dissatisfaction.</v>
       </c>
       <c r="J43" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K43" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
-        <v>High</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
       </c>
       <c r="L43" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/cebc8fcb-dd8e-43f7-a85e-b01e72f91582")</f>
-        <v>https://jam.dev/c/cebc8fcb-dd8e-43f7-a85e-b01e72f91582</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/eb37c560-e234-415b-95a6-f58bdb594cf8")</f>
+        <v>https://jam.dev/c/eb37c560-e234-415b-95a6-f58bdb594cf8</v>
       </c>
       <c r="M43" s="15"/>
       <c r="N43" s="13" t="s">
@@ -4578,47 +4692,38 @@
     </row>
     <row r="44">
       <c r="A44" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC (Brouser Dark Mode)
-Authentication ")</f>
-        <v>PC (Brouser Dark Mode)
-Authentication </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
       </c>
       <c r="C44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
-        <v>Login</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Landing Page")</f>
+        <v>Landing Page</v>
       </c>
       <c r="D44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify password field text color in dark mode is clearly visible")</f>
-        <v>Verify password field text color in dark mode is clearly visible</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The ""Read More"" option for the content under the banner is missing.")</f>
+        <v>The "Read More" option for the content under the banner is missing.</v>
       </c>
       <c r="E44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User's phone is in dark mode and user is on the login screen of the site")</f>
-        <v>User's phone is in dark mode and user is on the login screen of the site</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Ensure the phone is set to dark mode 
-3. Go to the login screen 
-4. Tap on the password field and type any text")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Ensure the phone is set to dark mode 
-3. Go to the login screen 
-4. Tap on the password field and type any text</v>
-      </c>
-      <c r="G44" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2. Scroll down to 2nd video")</f>
+        <v>1. Open VALR
+2. Scroll down to 2nd video</v>
+      </c>
+      <c r="G44" s="20"/>
       <c r="H44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The typed password should be clearly visible (e.g., light-colored text on dark background)")</f>
-        <v>The typed password should be clearly visible (e.g., light-colored text on dark background)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The stories banner should include a ""Read More"" option to allow users to view the full history.")</f>
+        <v>The stories banner should include a "Read More" option to allow users to view the full history.</v>
       </c>
       <c r="I44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Password text appears black on a dark background, making it hard to see")</f>
-        <v>Password text appears black on a dark background, making it hard to see</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Missing a ""Read More"" option in a story banner can make users believe the story is fake or created solely for publicity.")</f>
+        <v>Missing a "Read More" option in a story banner can make users believe the story is fake or created solely for publicity.</v>
       </c>
       <c r="J44" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4629,19 +4734,16 @@
         <v>High</v>
       </c>
       <c r="L44" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/d764618c-0455-4d4c-b1d0-2edb1a0f4428")</f>
-        <v>https://jam.dev/c/d764618c-0455-4d4c-b1d0-2edb1a0f4428</v>
-      </c>
-      <c r="M44" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)")</f>
-        <v>Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/421d8638-3a23-4a6c-b704-5362ff64b5dc")</f>
+        <v>https://jam.dev/c/421d8638-3a23-4a6c-b704-5362ff64b5dc</v>
+      </c>
+      <c r="M44" s="15"/>
       <c r="N44" s="13" t="s">
         <v>30</v>
       </c>
       <c r="O44" s="5"/>
       <c r="P44" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
@@ -4656,43 +4758,49 @@
     </row>
     <row r="45">
       <c r="A45" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignUp")</f>
-        <v>SignUp</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"
+Mobile Device
+Authentication (Dark Mode)")</f>
+        <v>
+Mobile Device
+Authentication (Dark Mode)</v>
       </c>
       <c r="C45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignUp")</f>
-        <v>SignUp</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
+        <v>Login</v>
       </c>
       <c r="D45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verifying user with an OTP has not been included for authentication.")</f>
-        <v>Verifying user with an OTP has not been included for authentication.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify password field text color in dark mode is clearly visible")</f>
+        <v>Verify password field text color in dark mode is clearly visible</v>
       </c>
       <c r="E45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User's phone is in dark mode and user is on the login screen of the site")</f>
+        <v>User's phone is in dark mode and user is on the login screen of the site</v>
       </c>
       <c r="F45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2.Goto Signup")</f>
-        <v>1. Open VALR
-2.Goto Signup</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Ensure the phone is set to dark mode 
+3. Go to the login screen 
+4. Tap on the password field and type any text")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Ensure the phone is set to dark mode 
+3. Go to the login screen 
+4. Tap on the password field and type any text</v>
       </c>
       <c r="G45" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678")</f>
-        <v>Email : tbfdmiyygildwxwqyp@nespf.com
-Pass : 12345678</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
       </c>
       <c r="H45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"After signing up, users should receive an OTP to ensure proper authentication for valid accounts.")</f>
-        <v>After signing up, users should receive an OTP to ensure proper authentication for valid accounts.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The typed password should be clearly visible (e.g., light-colored text on dark background)")</f>
+        <v>The typed password should be clearly visible (e.g., light-colored text on dark background)</v>
       </c>
       <c r="I45" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The app is missing OTP authentication.")</f>
-        <v>The app is missing OTP authentication.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Password text appears black on a dark background, making it hard to see")</f>
+        <v>Password text appears black on a dark background, making it hard to see</v>
       </c>
       <c r="J45" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4702,12 +4810,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
         <v>High</v>
       </c>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
+      <c r="L45" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/cca7d6de-4a27-4053-8108-3b660e26d30b")</f>
+        <v>https://jam.dev/c/cca7d6de-4a27-4053-8108-3b660e26d30b</v>
+      </c>
+      <c r="M45" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)")</f>
+        <v>Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)</v>
+      </c>
       <c r="N45" s="15"/>
       <c r="O45" s="5"/>
       <c r="P45" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
@@ -4722,45 +4836,38 @@
     </row>
     <row r="46">
       <c r="A46" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VAFORM")</f>
-        <v>VAFORM</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignIn")</f>
+        <v>SignIn</v>
       </c>
       <c r="C46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form PDFs")</f>
-        <v>VA Form PDFs</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
+        <v>Login</v>
       </c>
       <c r="D46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that the ""VA Form PDFs"" text is fully visible without being cut off")</f>
-        <v>Verify that the "VA Form PDFs" text is fully visible without being cut off</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The password hide icon overlaps when the user attempts to log in or signup")</f>
+        <v>The password hide icon overlaps when the user attempts to log in or signup</v>
       </c>
       <c r="E46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a mobile device and navigates to the VA Form section")</f>
-        <v>User is on a mobile device and navigates to the VA Form section</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
       </c>
       <c r="F46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
-2. Click to the VA Form section 
-3. Locate the text ""VA Form PDFs"" 
-4. Observe whether the full text is visible without being cut off")</f>
-        <v>1. Open https://valrpro.com/ on a mobile browser 
-2. Click to the VA Form section 
-3. Locate the text "VA Form PDFs" 
-4. Observe whether the full text is visible without being cut off</v>
-      </c>
-      <c r="G46" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
-        <v>N/A</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2.Goto Signin or signup")</f>
+        <v>1. Open VALR
+2.Goto Signin or signup</v>
+      </c>
+      <c r="G46" s="20"/>
       <c r="H46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text ""VA Form PDFs"" should be completely visible and properly aligned")</f>
-        <v>Text "VA Form PDFs" should be completely visible and properly aligned</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The visible and hide option icon for the password should remain consistent.")</f>
+        <v>The visible and hide option icon for the password should remain consistent.</v>
       </c>
       <c r="I46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text appears partially cut off or clipped on mobile screen")</f>
-        <v>Text appears partially cut off or clipped on mobile screen</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The icon overlaps when a user enters input in the password section.")</f>
+        <v>The icon overlaps when a user enters input in the password section.</v>
       </c>
       <c r="J46" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
@@ -4771,15 +4878,12 @@
         <v>Medium</v>
       </c>
       <c r="L46" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/04f6f0b1-1689-405a-9282-da51b68e4f80")</f>
-        <v>https://jam.dev/c/04f6f0b1-1689-405a-9282-da51b68e4f80</v>
-      </c>
-      <c r="M46" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Adjust responsive layout or padding to ensure full visibility of header text on all screen sizes")</f>
-        <v>Adjust responsive layout or padding to ensure full visibility of header text on all screen sizes</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/fec0b683-8105-450a-a86a-978e8e88eb6f")</f>
+        <v>https://jam.dev/c/fec0b683-8105-450a-a86a-978e8e88eb6f</v>
+      </c>
+      <c r="M46" s="15"/>
       <c r="N46" s="13" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
@@ -4796,52 +4900,54 @@
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignIn")</f>
+        <v>SignIn</v>
       </c>
       <c r="C47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video")</f>
-        <v>Video</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
+        <v>Login</v>
       </c>
       <c r="D47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video file corner are not same")</f>
-        <v>Video file corner are not same</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"When an unregistered user tries to log in, the prompt doesn't display ""Invalid email and password.""")</f>
+        <v>When an unregistered user tries to log in, the prompt doesn't display "Invalid email and password."</v>
       </c>
       <c r="E47" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
         <v>User should be able to be in browser</v>
       </c>
       <c r="F47" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR")</f>
-        <v>1. Open VALR</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2.Goto Signin or signup")</f>
+        <v>1. Open VALR
+2.Goto Signin or signup</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Corner of video file should be same ")</f>
-        <v>Corner of video file should be same </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"When an unregistered user attempts to log in to the system, the prompt should display a message indicating that the email is not registered in the system.")</f>
+        <v>When an unregistered user attempts to log in to the system, the prompt should display a message indicating that the email is not registered in the system.</v>
       </c>
       <c r="I47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Three corners are curved, but one is angled, leading to an unsatisfactory appearance.")</f>
-        <v>Three corners are curved, but one is angled, leading to an unsatisfactory appearance.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The prompt displays ""Something went wrong,"" but it doesn't clarify whether the issue is on the client side or due to a system error.")</f>
+        <v>The prompt displays "Something went wrong," but it doesn't clarify whether the issue is on the client side or due to a system error.</v>
       </c>
       <c r="J47" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K47" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L47" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/444699fc-345e-411f-a7c2-a455224996d7")</f>
-        <v>https://jam.dev/c/444699fc-345e-411f-a7c2-a455224996d7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/cebc8fcb-dd8e-43f7-a85e-b01e72f91582")</f>
+        <v>https://jam.dev/c/cebc8fcb-dd8e-43f7-a85e-b01e72f91582</v>
       </c>
       <c r="M47" s="15"/>
       <c r="N47" s="13" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
@@ -4858,58 +4964,70 @@
     </row>
     <row r="48">
       <c r="A48" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
-        <v>Home</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PC (Brouser Dark Mode)
+Authentication ")</f>
+        <v>PC (Brouser Dark Mode)
+Authentication </v>
       </c>
       <c r="C48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video")</f>
-        <v>Video</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Login")</f>
+        <v>Login</v>
       </c>
       <c r="D48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The border of the video file doesn't align with the Figma design.")</f>
-        <v>The border of the video file doesn't align with the Figma design.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify password field text color in dark mode is clearly visible")</f>
+        <v>Verify password field text color in dark mode is clearly visible</v>
       </c>
       <c r="E48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
-        <v>User should be able to be in browser</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User's phone is in dark mode and user is on the login screen of the site")</f>
+        <v>User's phone is in dark mode and user is on the login screen of the site</v>
       </c>
       <c r="F48" s="20" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
-2. Goto about VARL video")</f>
-        <v>1. Open VALR
-2. Goto about VARL video</v>
-      </c>
-      <c r="G48" s="20"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Ensure the phone is set to dark mode 
+3. Go to the login screen 
+4. Tap on the password field and type any text")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Ensure the phone is set to dark mode 
+3. Go to the login screen 
+4. Tap on the password field and type any text</v>
+      </c>
+      <c r="G48" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
       <c r="H48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video shade design should match the client's requirements exactly.")</f>
-        <v>The video shade design should match the client's requirements exactly.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The typed password should be clearly visible (e.g., light-colored text on dark background)")</f>
+        <v>The typed password should be clearly visible (e.g., light-colored text on dark background)</v>
       </c>
       <c r="I48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A deviation from the client's requirements has been observed.")</f>
-        <v>A deviation from the client's requirements has been observed.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Password text appears black on a dark background, making it hard to see")</f>
+        <v>Password text appears black on a dark background, making it hard to see</v>
       </c>
       <c r="J48" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
         <v>Fail</v>
       </c>
       <c r="K48" s="15" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
-        <v>Low</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
       </c>
       <c r="L48" s="19" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/842807bd-0b79-48a9-b2ce-d1be28607e80")</f>
-        <v>https://jam.dev/c/842807bd-0b79-48a9-b2ce-d1be28607e80</v>
-      </c>
-      <c r="M48" s="15"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/d764618c-0455-4d4c-b1d0-2edb1a0f4428")</f>
+        <v>https://jam.dev/c/d764618c-0455-4d4c-b1d0-2edb1a0f4428</v>
+      </c>
+      <c r="M48" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)")</f>
+        <v>Update input field CSS to ensure sufficient color contrast for dark mode (e.g., use light-colored text)</v>
+      </c>
       <c r="N48" s="13" t="s">
         <v>30</v>
       </c>
       <c r="O48" s="5"/>
       <c r="P48" s="22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
@@ -4924,19 +5042,58 @@
     </row>
     <row r="49">
       <c r="A49" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
+        <v>76</v>
+      </c>
+      <c r="B49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
+      </c>
+      <c r="C49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mental_health_details")</f>
+        <v>mental_health_details</v>
+      </c>
+      <c r="D49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An alignment issue has been observed.")</f>
+        <v>An alignment issue has been observed.</v>
+      </c>
+      <c r="E49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
+      </c>
+      <c r="F49" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 12th steps ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 12th steps </v>
+      </c>
+      <c r="G49" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
+      </c>
+      <c r="H49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Proper page alignment should always be maintained.")</f>
+        <v>Proper page alignment should always be maintained.</v>
+      </c>
+      <c r="I49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"An issue with alignment breakdown has been identified.")</f>
+        <v>An issue with alignment breakdown has been identified.</v>
+      </c>
+      <c r="J49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K49" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="L49" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/1b388bd9-a49f-4563-8345-8671539786f6")</f>
+        <v>https://jam.dev/c/1b388bd9-a49f-4563-8345-8671539786f6</v>
+      </c>
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
       <c r="O49" s="5"/>
@@ -4954,19 +5111,58 @@
     </row>
     <row r="50">
       <c r="A50" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
+        <v>77</v>
+      </c>
+      <c r="B50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form")</f>
+        <v>VA Form</v>
+      </c>
+      <c r="C50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mental_health_info")</f>
+        <v>mental_health_info</v>
+      </c>
+      <c r="D50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Work period time is not clearly specified as per day or total service hours.")</f>
+        <v>Work period time is not clearly specified as per day or total service hours.</v>
+      </c>
+      <c r="E50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
+      </c>
+      <c r="F50" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 12th steps ")</f>
+        <v>1. Open VALR.  
+2. Sign in using valid credentials.
+3. Click on VA form and filled up to 12th steps </v>
+      </c>
+      <c r="G50" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : bijoymamud.09@gmail.com
+Pass : 12345678")</f>
+        <v>Email : bijoymamud.09@gmail.com
+Pass : 12345678</v>
+      </c>
+      <c r="H50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Veterans' work period should be clearly specified as either daily hours or total service hours.")</f>
+        <v>Veterans' work period should be clearly specified as either daily hours or total service hours.</v>
+      </c>
+      <c r="I50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The lack of proper information has been noticed, which can sometimes lead to confusion for some veterans.")</f>
+        <v>The lack of proper information has been noticed, which can sometimes lead to confusion for some veterans.</v>
+      </c>
+      <c r="J50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K50" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
+      </c>
+      <c r="L50" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/4fedc7b2-3f23-42bf-b95c-8315a5122b20")</f>
+        <v>https://jam.dev/c/4fedc7b2-3f23-42bf-b95c-8315a5122b20</v>
+      </c>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
       <c r="O50" s="5"/>
@@ -4984,18 +5180,52 @@
     </row>
     <row r="51">
       <c r="A51" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
+        <v>78</v>
+      </c>
+      <c r="B51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignUp")</f>
+        <v>SignUp</v>
+      </c>
+      <c r="C51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SignUp")</f>
+        <v>SignUp</v>
+      </c>
+      <c r="D51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verifying user with an OTP has not been included for authentication.")</f>
+        <v>Verifying user with an OTP has not been included for authentication.</v>
+      </c>
+      <c r="E51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
+      </c>
+      <c r="F51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2.Goto Signup")</f>
+        <v>1. Open VALR
+2.Goto Signup</v>
+      </c>
+      <c r="G51" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678")</f>
+        <v>Email : tbfdmiyygildwxwqyp@nespf.com
+Pass : 12345678</v>
+      </c>
+      <c r="H51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"After signing up, users should receive an OTP to ensure proper authentication for valid accounts.")</f>
+        <v>After signing up, users should receive an OTP to ensure proper authentication for valid accounts.</v>
+      </c>
+      <c r="I51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The app is missing OTP authentication.")</f>
+        <v>The app is missing OTP authentication.</v>
+      </c>
+      <c r="J51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K51" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"High")</f>
+        <v>High</v>
+      </c>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
@@ -5014,20 +5244,62 @@
     </row>
     <row r="52">
       <c r="A52" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
+        <v>79</v>
+      </c>
+      <c r="B52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VAFORM")</f>
+        <v>VAFORM</v>
+      </c>
+      <c r="C52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VA Form PDFs")</f>
+        <v>VA Form PDFs</v>
+      </c>
+      <c r="D52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Verify that the ""VA Form PDFs"" text is fully visible without being cut off")</f>
+        <v>Verify that the "VA Form PDFs" text is fully visible without being cut off</v>
+      </c>
+      <c r="E52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User is on a mobile device and navigates to the VA Form section")</f>
+        <v>User is on a mobile device and navigates to the VA Form section</v>
+      </c>
+      <c r="F52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open https://valrpro.com/ on a mobile browser 
+2. Click to the VA Form section 
+3. Locate the text ""VA Form PDFs"" 
+4. Observe whether the full text is visible without being cut off")</f>
+        <v>1. Open https://valrpro.com/ on a mobile browser 
+2. Click to the VA Form section 
+3. Locate the text "VA Form PDFs" 
+4. Observe whether the full text is visible without being cut off</v>
+      </c>
+      <c r="G52" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="H52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text ""VA Form PDFs"" should be completely visible and properly aligned")</f>
+        <v>Text "VA Form PDFs" should be completely visible and properly aligned</v>
+      </c>
+      <c r="I52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Text appears partially cut off or clipped on mobile screen")</f>
+        <v>Text appears partially cut off or clipped on mobile screen</v>
+      </c>
+      <c r="J52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Medium")</f>
+        <v>Medium</v>
+      </c>
+      <c r="L52" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/04f6f0b1-1689-405a-9282-da51b68e4f80")</f>
+        <v>https://jam.dev/c/04f6f0b1-1689-405a-9282-da51b68e4f80</v>
+      </c>
+      <c r="M52" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Adjust responsive layout or padding to ensure full visibility of header text on all screen sizes")</f>
+        <v>Adjust responsive layout or padding to ensure full visibility of header text on all screen sizes</v>
+      </c>
       <c r="N52" s="15"/>
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
@@ -5044,19 +5316,49 @@
     </row>
     <row r="53">
       <c r="A53" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="B53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
+      </c>
+      <c r="C53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video")</f>
+        <v>Video</v>
+      </c>
+      <c r="D53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video file corner are not same")</f>
+        <v>Video file corner are not same</v>
+      </c>
+      <c r="E53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
+      </c>
+      <c r="F53" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR")</f>
+        <v>1. Open VALR</v>
+      </c>
       <c r="G53" s="20"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
+      <c r="H53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Corner of video file should be same ")</f>
+        <v>Corner of video file should be same </v>
+      </c>
+      <c r="I53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Three corners are curved, but one is angled, leading to an unsatisfactory appearance.")</f>
+        <v>Three corners are curved, but one is angled, leading to an unsatisfactory appearance.</v>
+      </c>
+      <c r="J53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K53" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="L53" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/444699fc-345e-411f-a7c2-a455224996d7")</f>
+        <v>https://jam.dev/c/444699fc-345e-411f-a7c2-a455224996d7</v>
+      </c>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
       <c r="O53" s="5"/>
@@ -5074,19 +5376,51 @@
     </row>
     <row r="54">
       <c r="A54" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="20"/>
+        <v>81</v>
+      </c>
+      <c r="B54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Home")</f>
+        <v>Home</v>
+      </c>
+      <c r="C54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Video")</f>
+        <v>Video</v>
+      </c>
+      <c r="D54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The border of the video file doesn't align with the Figma design.")</f>
+        <v>The border of the video file doesn't align with the Figma design.</v>
+      </c>
+      <c r="E54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"User should be able to be in browser")</f>
+        <v>User should be able to be in browser</v>
+      </c>
+      <c r="F54" s="20" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1. Open VALR
+2. Goto about VARL video")</f>
+        <v>1. Open VALR
+2. Goto about VARL video</v>
+      </c>
       <c r="G54" s="20"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
+      <c r="H54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"The video shade design should match the client's requirements exactly.")</f>
+        <v>The video shade design should match the client's requirements exactly.</v>
+      </c>
+      <c r="I54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"A deviation from the client's requirements has been observed.")</f>
+        <v>A deviation from the client's requirements has been observed.</v>
+      </c>
+      <c r="J54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fail")</f>
+        <v>Fail</v>
+      </c>
+      <c r="K54" s="15" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="L54" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"https://jam.dev/c/842807bd-0b79-48a9-b2ce-d1be28607e80")</f>
+        <v>https://jam.dev/c/842807bd-0b79-48a9-b2ce-d1be28607e80</v>
+      </c>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
       <c r="O54" s="5"/>
@@ -5104,7 +5438,7 @@
     </row>
     <row r="55">
       <c r="A55" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -5134,7 +5468,7 @@
     </row>
     <row r="56">
       <c r="A56" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -5164,7 +5498,7 @@
     </row>
     <row r="57">
       <c r="A57" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -5194,7 +5528,7 @@
     </row>
     <row r="58">
       <c r="A58" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -5224,7 +5558,7 @@
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -5254,7 +5588,7 @@
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -5284,7 +5618,7 @@
     </row>
     <row r="61">
       <c r="A61" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -5314,7 +5648,7 @@
     </row>
     <row r="62">
       <c r="A62" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -5344,7 +5678,7 @@
     </row>
     <row r="63">
       <c r="A63" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -5374,7 +5708,7 @@
     </row>
     <row r="64">
       <c r="A64" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -5404,7 +5738,7 @@
     </row>
     <row r="65">
       <c r="A65" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -5434,7 +5768,7 @@
     </row>
     <row r="66">
       <c r="A66" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -5464,7 +5798,7 @@
     </row>
     <row r="67">
       <c r="A67" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -5494,7 +5828,7 @@
     </row>
     <row r="68">
       <c r="A68" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -5524,7 +5858,7 @@
     </row>
     <row r="69">
       <c r="A69" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -5554,7 +5888,7 @@
     </row>
     <row r="70">
       <c r="A70" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -5584,7 +5918,7 @@
     </row>
     <row r="71">
       <c r="A71" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -5614,7 +5948,7 @@
     </row>
     <row r="72">
       <c r="A72" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -5644,7 +5978,7 @@
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -5674,7 +6008,7 @@
     </row>
     <row r="74">
       <c r="A74" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -5704,7 +6038,7 @@
     </row>
     <row r="75">
       <c r="A75" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -5734,7 +6068,7 @@
     </row>
     <row r="76">
       <c r="A76" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -5764,7 +6098,7 @@
     </row>
     <row r="77">
       <c r="A77" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -5794,7 +6128,7 @@
     </row>
     <row r="78">
       <c r="A78" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -5824,7 +6158,7 @@
     </row>
     <row r="79">
       <c r="A79" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -5854,7 +6188,7 @@
     </row>
     <row r="80">
       <c r="A80" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -5884,7 +6218,7 @@
     </row>
     <row r="81">
       <c r="A81" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -5914,7 +6248,7 @@
     </row>
     <row r="82">
       <c r="A82" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -5944,7 +6278,7 @@
     </row>
     <row r="83">
       <c r="A83" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -5974,7 +6308,7 @@
     </row>
     <row r="84">
       <c r="A84" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -6004,7 +6338,7 @@
     </row>
     <row r="85">
       <c r="A85" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -6034,7 +6368,7 @@
     </row>
     <row r="86">
       <c r="A86" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -6064,7 +6398,7 @@
     </row>
     <row r="87">
       <c r="A87" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -6094,7 +6428,7 @@
     </row>
     <row r="88">
       <c r="A88" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -6124,7 +6458,7 @@
     </row>
     <row r="89">
       <c r="A89" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -6154,7 +6488,7 @@
     </row>
     <row r="90">
       <c r="A90" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -27565,11 +27899,17 @@
     <hyperlink r:id="rId32" ref="L42"/>
     <hyperlink r:id="rId33" ref="L43"/>
     <hyperlink r:id="rId34" ref="L44"/>
-    <hyperlink r:id="rId35" ref="L46"/>
-    <hyperlink r:id="rId36" ref="L47"/>
-    <hyperlink r:id="rId37" ref="L48"/>
+    <hyperlink r:id="rId35" ref="L45"/>
+    <hyperlink r:id="rId36" ref="L46"/>
+    <hyperlink r:id="rId37" ref="L47"/>
+    <hyperlink r:id="rId38" ref="L48"/>
+    <hyperlink r:id="rId39" ref="L49"/>
+    <hyperlink r:id="rId40" ref="L50"/>
+    <hyperlink r:id="rId41" ref="L52"/>
+    <hyperlink r:id="rId42" ref="L53"/>
+    <hyperlink r:id="rId43" ref="L54"/>
   </hyperlinks>
-  <drawing r:id="rId38"/>
+  <drawing r:id="rId44"/>
 </worksheet>
 </file>
 
@@ -27628,7 +27968,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="8" t="s">
@@ -27664,7 +28004,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="11" t="s">
@@ -27672,7 +28012,7 @@
       </c>
       <c r="E3" s="32">
         <f>COUNTIF(K14:K1005, "High") + COUNTIF(Fahad!K9:K1002, "High")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
@@ -27701,7 +28041,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="11" t="s">
@@ -27709,7 +28049,7 @@
       </c>
       <c r="E4" s="32">
         <f>COUNTIF(K14:K1006, "Medium") + COUNTIF(Fahad!K9:K1003, "Medium")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="27"/>
@@ -27744,7 +28084,7 @@
       </c>
       <c r="E5" s="32">
         <f>COUNTIF(K14:K1007, "Low") + COUNTIF(Fahad!K9:K1004, "Low")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" s="27"/>
       <c r="H5" s="27"/>
@@ -27806,7 +28146,7 @@
       </c>
       <c r="E7" s="38">
         <f>SUM(E3:E5)</f>
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -27875,160 +28215,160 @@
     <row r="15">
       <c r="A15" s="41"/>
       <c r="B15" s="42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K15" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M15" s="41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N15" s="41"/>
     </row>
     <row r="16">
       <c r="A16" s="41"/>
       <c r="B16" s="42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K16" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M16" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N16" s="44"/>
     </row>
     <row r="17">
       <c r="A17" s="41"/>
       <c r="B17" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F17" s="45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G17" s="45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H17" s="45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I17" s="45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K17" s="45" t="s">
         <v>11</v>
       </c>
       <c r="L17" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N17" s="47"/>
     </row>
     <row r="18">
       <c r="A18" s="41"/>
       <c r="B18" s="42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H18" s="41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K18" s="41" t="s">
         <v>6</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M18" s="41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N18" s="44"/>
     </row>
@@ -29409,7 +29749,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="8" t="s">
@@ -29445,7 +29785,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="11" t="s">
@@ -29453,7 +29793,7 @@
       </c>
       <c r="E3" s="32">
         <f>COUNTIF(K14:K1008, "High") + COUNTIF(Fahad!K9:K1002, "High")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
@@ -29482,7 +29822,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="11" t="s">
@@ -29490,7 +29830,7 @@
       </c>
       <c r="E4" s="32">
         <f>COUNTIF(K14:K1009, "Medium") + COUNTIF(Fahad!K9:K1003, "Medium")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="27"/>
@@ -29525,7 +29865,7 @@
       </c>
       <c r="E5" s="32">
         <f>COUNTIF(K14:K1010, "Low") + COUNTIF(Fahad!K9:K1004, "Low")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="27"/>
       <c r="H5" s="27"/>
@@ -29587,7 +29927,7 @@
       </c>
       <c r="E7" s="38">
         <f>SUM(E3:E5)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -29656,77 +29996,77 @@
     <row r="15">
       <c r="A15" s="41"/>
       <c r="B15" s="42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K15" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M15" s="41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N15" s="44"/>
     </row>
     <row r="16">
       <c r="A16" s="41"/>
       <c r="B16" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K16" s="41" t="s">
         <v>11</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M16" s="41"/>
       <c r="N16" s="44"/>
@@ -29734,37 +30074,37 @@
     <row r="17">
       <c r="A17" s="41"/>
       <c r="B17" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G17" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H17" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I17" s="41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K17" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L17" s="43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="44"/>
@@ -29772,37 +30112,37 @@
     <row r="18">
       <c r="A18" s="41"/>
       <c r="B18" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H18" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K18" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M18" s="41"/>
       <c r="N18" s="44"/>
@@ -29810,37 +30150,37 @@
     <row r="19">
       <c r="A19" s="41"/>
       <c r="B19" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H19" s="41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K19" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L19" s="43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M19" s="41"/>
       <c r="N19" s="44"/>
@@ -29848,160 +30188,160 @@
     <row r="20">
       <c r="A20" s="41"/>
       <c r="B20" s="42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K20" s="41" t="s">
         <v>11</v>
       </c>
       <c r="L20" s="43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M20" s="41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N20" s="44"/>
     </row>
     <row r="21">
       <c r="A21" s="41"/>
       <c r="B21" s="42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K21" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M21" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N21" s="44"/>
     </row>
     <row r="22">
       <c r="A22" s="41"/>
       <c r="B22" s="42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K22" s="41" t="s">
         <v>6</v>
       </c>
       <c r="L22" s="43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M22" s="41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="44"/>
     </row>
     <row r="23">
       <c r="A23" s="41"/>
       <c r="B23" s="42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K23" s="41" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M23" s="41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N23" s="44"/>
     </row>
@@ -31353,7 +31693,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
@@ -31385,7 +31725,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -31447,7 +31787,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
@@ -31479,7 +31819,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
@@ -31536,7 +31876,7 @@
     </row>
     <row r="8">
       <c r="A8" s="59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>17</v>
@@ -31595,35 +31935,35 @@
         <v>29</v>
       </c>
       <c r="B9" s="61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E9" s="61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F9" s="62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G9" s="63"/>
       <c r="H9" s="61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I9" s="61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J9" s="61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K9" s="61" t="s">
         <v>11</v>
       </c>
       <c r="L9" s="64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M9" s="65"/>
       <c r="N9" s="61"/>
@@ -31673,35 +32013,35 @@
         <v>31</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D11" s="68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E11" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F11" s="69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" s="49"/>
       <c r="H11" s="68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I11" s="68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J11" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K11" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L11" s="70" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M11" s="71"/>
       <c r="N11" s="71"/>
@@ -31751,35 +32091,35 @@
         <v>32</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D13" s="68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F13" s="69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G13" s="49"/>
       <c r="H13" s="68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I13" s="68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J13" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K13" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L13" s="70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M13" s="71"/>
       <c r="N13" s="71"/>
@@ -31829,35 +32169,35 @@
         <v>33</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F15" s="69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G15" s="49"/>
       <c r="H15" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I15" s="68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J15" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K15" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
@@ -31907,35 +32247,35 @@
         <v>34</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G17" s="72"/>
       <c r="H17" s="68" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I17" s="68" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J17" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K17" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L17" s="70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M17" s="71"/>
       <c r="N17" s="71"/>
@@ -31985,35 +32325,35 @@
         <v>35</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D19" s="68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F19" s="69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G19" s="72"/>
       <c r="H19" s="68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I19" s="68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J19" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K19" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L19" s="70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M19" s="71"/>
       <c r="N19" s="71"/>
@@ -32063,35 +32403,35 @@
         <v>36</v>
       </c>
       <c r="B21" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D21" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F21" s="69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G21" s="72"/>
       <c r="H21" s="68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I21" s="68" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J21" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K21" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M21" s="71"/>
       <c r="N21" s="71"/>
@@ -32141,35 +32481,35 @@
         <v>37</v>
       </c>
       <c r="B23" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D23" s="68" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F23" s="69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G23" s="72"/>
       <c r="H23" s="68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I23" s="68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J23" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K23" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" s="71"/>
       <c r="N23" s="71"/>
@@ -32219,35 +32559,35 @@
         <v>38</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D25" s="68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F25" s="69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G25" s="49"/>
       <c r="H25" s="68" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I25" s="68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J25" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K25" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L25" s="70" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" s="71"/>
       <c r="N25" s="71"/>
@@ -32297,35 +32637,35 @@
         <v>39</v>
       </c>
       <c r="B27" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D27" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F27" s="69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G27" s="49"/>
       <c r="H27" s="68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I27" s="68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J27" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K27" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L27" s="70" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M27" s="71"/>
       <c r="N27" s="71"/>
@@ -32372,38 +32712,38 @@
     </row>
     <row r="29">
       <c r="A29" s="68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D29" s="68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F29" s="69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G29" s="72"/>
       <c r="H29" s="68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I29" s="68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J29" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K29" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L29" s="70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M29" s="71"/>
       <c r="N29" s="71"/>
@@ -32450,38 +32790,38 @@
     </row>
     <row r="31">
       <c r="A31" s="68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F31" s="69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G31" s="49"/>
       <c r="H31" s="68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I31" s="68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J31" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K31" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L31" s="74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M31" s="71"/>
       <c r="N31" s="71"/>
@@ -32528,38 +32868,38 @@
     </row>
     <row r="33">
       <c r="A33" s="68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" s="68" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F33" s="69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G33" s="49"/>
       <c r="H33" s="68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I33" s="68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J33" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K33" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L33" s="70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M33" s="71"/>
       <c r="N33" s="71"/>
@@ -32606,38 +32946,38 @@
     </row>
     <row r="35">
       <c r="A35" s="68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D35" s="68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E35" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G35" s="49"/>
       <c r="H35" s="68" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I35" s="68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J35" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K35" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L35" s="76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M35" s="71"/>
       <c r="N35" s="71"/>
@@ -32684,38 +33024,38 @@
     </row>
     <row r="37">
       <c r="A37" s="68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D37" s="68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E37" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37" s="69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G37" s="49"/>
       <c r="H37" s="68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I37" s="68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J37" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K37" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L37" s="70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M37" s="71"/>
       <c r="N37" s="71"/>
@@ -32738,7 +33078,7 @@
       <c r="C38" s="66"/>
       <c r="D38" s="66"/>
       <c r="E38" s="75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F38" s="66"/>
       <c r="G38" s="66"/>
@@ -32764,38 +33104,38 @@
     </row>
     <row r="39">
       <c r="A39" s="68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C39" s="68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D39" s="68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G39" s="49"/>
       <c r="H39" s="68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I39" s="68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J39" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K39" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L39" s="70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M39" s="71"/>
       <c r="N39" s="71"/>
@@ -32842,34 +33182,34 @@
     </row>
     <row r="41">
       <c r="A41" s="68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="68" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C41" s="68" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H41" s="68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I41" s="68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J41" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K41" s="68" t="s">
         <v>6</v>
@@ -32920,40 +33260,40 @@
     </row>
     <row r="43">
       <c r="A43" s="68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" s="68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D43" s="68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G43" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H43" s="68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I43" s="68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J43" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K43" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L43" s="77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M43" s="71"/>
       <c r="N43" s="71"/>
@@ -33000,40 +33340,40 @@
     </row>
     <row r="45">
       <c r="A45" s="68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C45" s="68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D45" s="68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E45" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F45" s="69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G45" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H45" s="68" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I45" s="68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J45" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K45" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L45" s="70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M45" s="71"/>
       <c r="N45" s="71"/>
@@ -33080,40 +33420,40 @@
     </row>
     <row r="47">
       <c r="A47" s="68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B47" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D47" s="68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E47" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F47" s="69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G47" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H47" s="68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I47" s="68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J47" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K47" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L47" s="70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M47" s="68"/>
       <c r="N47" s="71"/>
@@ -33160,40 +33500,40 @@
     </row>
     <row r="49">
       <c r="A49" s="68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B49" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C49" s="68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E49" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F49" s="69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G49" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H49" s="68" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I49" s="68" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J49" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K49" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L49" s="70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M49" s="71"/>
       <c r="N49" s="71"/>
@@ -33240,40 +33580,40 @@
     </row>
     <row r="51">
       <c r="A51" s="68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C51" s="68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D51" s="68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E51" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F51" s="69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G51" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H51" s="68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I51" s="68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J51" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K51" s="68" t="s">
         <v>9</v>
       </c>
       <c r="L51" s="70" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M51" s="71"/>
       <c r="N51" s="71"/>
@@ -33320,40 +33660,40 @@
     </row>
     <row r="53">
       <c r="A53" s="68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C53" s="68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D53" s="68" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E53" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F53" s="69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G53" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H53" s="68" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I53" s="68" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J53" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K53" s="68" t="s">
         <v>11</v>
       </c>
       <c r="L53" s="70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M53" s="71"/>
       <c r="N53" s="71"/>
@@ -33400,40 +33740,40 @@
     </row>
     <row r="55">
       <c r="A55" s="68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55" s="68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C55" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D55" s="68" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E55" s="68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="69" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G55" s="49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H55" s="68" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I55" s="68" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J55" s="68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K55" s="68" t="s">
         <v>6</v>
       </c>
       <c r="L55" s="70" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M55" s="71"/>
       <c r="N55" s="71"/>
@@ -33480,21 +33820,45 @@
     </row>
     <row r="57">
       <c r="A57" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="68"/>
-      <c r="L57" s="66"/>
-      <c r="M57" s="66"/>
-      <c r="N57" s="71"/>
+        <v>59</v>
+      </c>
+      <c r="B57" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="D57" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="E57" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F57" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="G57" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H57" s="68" t="s">
+        <v>328</v>
+      </c>
+      <c r="I57" s="68" t="s">
+        <v>329</v>
+      </c>
+      <c r="J57" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K57" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="L57" s="70" t="s">
+        <v>330</v>
+      </c>
+      <c r="M57" s="71"/>
+      <c r="N57" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O57" s="66"/>
       <c r="P57" s="66"/>
       <c r="Q57" s="66"/>
@@ -33537,20 +33901,46 @@
       <c r="Z58" s="66"/>
     </row>
     <row r="59">
-      <c r="A59" s="68"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="66"/>
-      <c r="M59" s="66"/>
-      <c r="N59" s="71"/>
+      <c r="A59" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="68" t="s">
+        <v>332</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E59" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="G59" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H59" s="68" t="s">
+        <v>335</v>
+      </c>
+      <c r="I59" s="68" t="s">
+        <v>336</v>
+      </c>
+      <c r="J59" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K59" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="L59" s="70" t="s">
+        <v>337</v>
+      </c>
+      <c r="M59" s="71"/>
+      <c r="N59" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O59" s="66"/>
       <c r="P59" s="66"/>
       <c r="Q59" s="66"/>
@@ -33593,20 +33983,46 @@
       <c r="Z60" s="66"/>
     </row>
     <row r="61">
-      <c r="A61" s="68"/>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="66"/>
-      <c r="M61" s="66"/>
-      <c r="N61" s="71"/>
+      <c r="A61" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>338</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="E61" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="G61" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H61" s="68" t="s">
+        <v>339</v>
+      </c>
+      <c r="I61" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="J61" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K61" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="L61" s="70" t="s">
+        <v>341</v>
+      </c>
+      <c r="M61" s="71"/>
+      <c r="N61" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O61" s="66"/>
       <c r="P61" s="66"/>
       <c r="Q61" s="66"/>
@@ -33649,20 +34065,46 @@
       <c r="Z62" s="66"/>
     </row>
     <row r="63">
-      <c r="A63" s="68"/>
-      <c r="B63" s="66"/>
-      <c r="C63" s="66"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="66"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
-      <c r="H63" s="66"/>
-      <c r="I63" s="66"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="66"/>
-      <c r="M63" s="66"/>
-      <c r="N63" s="71"/>
+      <c r="A63" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="D63" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="E63" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F63" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="G63" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H63" s="68" t="s">
+        <v>339</v>
+      </c>
+      <c r="I63" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="J63" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K63" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="L63" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="M63" s="71"/>
+      <c r="N63" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O63" s="66"/>
       <c r="P63" s="66"/>
       <c r="Q63" s="66"/>
@@ -33705,20 +34147,46 @@
       <c r="Z64" s="66"/>
     </row>
     <row r="65">
-      <c r="A65" s="68"/>
-      <c r="B65" s="66"/>
-      <c r="C65" s="66"/>
-      <c r="D65" s="66"/>
-      <c r="E65" s="66"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-      <c r="H65" s="66"/>
-      <c r="I65" s="66"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="68"/>
-      <c r="L65" s="66"/>
-      <c r="M65" s="66"/>
-      <c r="N65" s="71"/>
+      <c r="A65" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C65" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>346</v>
+      </c>
+      <c r="E65" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F65" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="G65" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H65" s="68" t="s">
+        <v>347</v>
+      </c>
+      <c r="I65" s="68" t="s">
+        <v>348</v>
+      </c>
+      <c r="J65" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K65" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="L65" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="M65" s="71"/>
+      <c r="N65" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O65" s="66"/>
       <c r="P65" s="66"/>
       <c r="Q65" s="66"/>
@@ -33761,20 +34229,46 @@
       <c r="Z66" s="66"/>
     </row>
     <row r="67">
-      <c r="A67" s="68"/>
-      <c r="B67" s="66"/>
-      <c r="C67" s="66"/>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="68"/>
-      <c r="K67" s="68"/>
-      <c r="L67" s="66"/>
-      <c r="M67" s="66"/>
-      <c r="N67" s="71"/>
+      <c r="A67" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="C67" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="D67" s="68" t="s">
+        <v>346</v>
+      </c>
+      <c r="E67" s="68" t="s">
+        <v>207</v>
+      </c>
+      <c r="F67" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="G67" s="49" t="s">
+        <v>327</v>
+      </c>
+      <c r="H67" s="68" t="s">
+        <v>350</v>
+      </c>
+      <c r="I67" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="J67" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="K67" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="L67" s="70" t="s">
+        <v>352</v>
+      </c>
+      <c r="M67" s="71"/>
+      <c r="N67" s="68" t="s">
+        <v>331</v>
+      </c>
       <c r="O67" s="66"/>
       <c r="P67" s="66"/>
       <c r="Q67" s="66"/>
@@ -33818,8 +34312,8 @@
     </row>
     <row r="69">
       <c r="A69" s="68"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
       <c r="D69" s="66"/>
       <c r="E69" s="66"/>
       <c r="F69" s="67"/>
@@ -60145,7 +60639,13 @@
     <hyperlink r:id="rId22" ref="L51"/>
     <hyperlink r:id="rId23" ref="L53"/>
     <hyperlink r:id="rId24" ref="L55"/>
+    <hyperlink r:id="rId25" ref="L57"/>
+    <hyperlink r:id="rId26" ref="L59"/>
+    <hyperlink r:id="rId27" ref="L61"/>
+    <hyperlink r:id="rId28" ref="L63"/>
+    <hyperlink r:id="rId29" ref="L65"/>
+    <hyperlink r:id="rId30" ref="L67"/>
   </hyperlinks>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>